--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Southenergy Spa Dropbox\Project Activos PV\20 - Análisis\Análisis centrales\Resultados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_11358078367124219904/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F275FB-DE7A-43AA-BAAA-674B50A9D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{56F275FB-DE7A-43AA-BAAA-674B50A9D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC80A84-A78D-4B7F-A4DB-B882D25AF553}"/>
   <bookViews>
-    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking PFV" sheetId="5" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -245,14 +245,20 @@
   <si>
     <t>Score Comercial Promedio</t>
   </si>
+  <si>
+    <t>Score Técnico Promedio 2025</t>
+  </si>
+  <si>
+    <t>Propietario</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="169" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -371,7 +377,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -385,13 +391,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -455,6 +461,9 @@
     <sheetDataSet>
       <sheetData sheetId="0">
         <row r="3">
+          <cell r="C3" t="str">
+            <v>GR CHAÑAR SPA</v>
+          </cell>
           <cell r="D3" t="str">
             <v>PFV VICTOR JARA</v>
           </cell>
@@ -466,6 +475,9 @@
           </cell>
         </row>
         <row r="4">
+          <cell r="C4" t="str">
+            <v>ANDES SOLAR III SPA</v>
+          </cell>
           <cell r="D4" t="str">
             <v>PFV ANDES SOLAR III</v>
           </cell>
@@ -477,6 +489,9 @@
           </cell>
         </row>
         <row r="5">
+          <cell r="C5" t="str">
+            <v>GR PIÑOL SPA</v>
+          </cell>
           <cell r="D5" t="str">
             <v>PFV CALEU</v>
           </cell>
@@ -488,6 +503,9 @@
           </cell>
         </row>
         <row r="6">
+          <cell r="C6" t="str">
+            <v>GR ALGARROBO SPA</v>
+          </cell>
           <cell r="D6" t="str">
             <v>PFV GRAN TENO</v>
           </cell>
@@ -499,6 +517,9 @@
           </cell>
         </row>
         <row r="7">
+          <cell r="C7" t="str">
+            <v>ANDES SOLAR II SPA</v>
+          </cell>
           <cell r="D7" t="str">
             <v>PFV ANDES SOLAR II</v>
           </cell>
@@ -510,6 +531,9 @@
           </cell>
         </row>
         <row r="8">
+          <cell r="C8" t="str">
+            <v>ENGIE ENERGÍA CHILE S.A.</v>
+          </cell>
           <cell r="D8" t="str">
             <v>PFV TAMAYA SOLAR</v>
           </cell>
@@ -521,6 +545,9 @@
           </cell>
         </row>
         <row r="9">
+          <cell r="C9" t="str">
+            <v>DOÑA ANTONIA SOLAR SPA</v>
+          </cell>
           <cell r="D9" t="str">
             <v>PFV DOÑA ANTONIA</v>
           </cell>
@@ -532,6 +559,9 @@
           </cell>
         </row>
         <row r="10">
+          <cell r="C10" t="str">
+            <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+          </cell>
           <cell r="D10" t="str">
             <v>PFV DIEGO DE ALMAGRO</v>
           </cell>
@@ -543,6 +573,9 @@
           </cell>
         </row>
         <row r="11">
+          <cell r="C11" t="str">
+            <v>ENERGÍA CERRO EL MORADO S.A.</v>
+          </cell>
           <cell r="D11" t="str">
             <v>PFV DOÑA CARMEN SOLAR</v>
           </cell>
@@ -554,6 +587,9 @@
           </cell>
         </row>
         <row r="12">
+          <cell r="C12" t="str">
+            <v>ENLIGHT INVESTMENTS SPA</v>
+          </cell>
           <cell r="D12" t="str">
             <v>PFV LA HUAYCA II</v>
           </cell>
@@ -565,6 +601,9 @@
           </cell>
         </row>
         <row r="13">
+          <cell r="C13" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D13" t="str">
             <v>PFV CHAÑARES</v>
           </cell>
@@ -576,6 +615,9 @@
           </cell>
         </row>
         <row r="14">
+          <cell r="C14" t="str">
+            <v>GENERACIÓN SOLAR SPA</v>
+          </cell>
           <cell r="D14" t="str">
             <v>PFV MARIA ELENA</v>
           </cell>
@@ -587,6 +629,9 @@
           </cell>
         </row>
         <row r="15">
+          <cell r="C15" t="str">
+            <v>CHUNGUNGO S.A.</v>
+          </cell>
           <cell r="D15" t="str">
             <v>PFV QUILAPILUN</v>
           </cell>
@@ -598,6 +643,9 @@
           </cell>
         </row>
         <row r="16">
+          <cell r="C16" t="str">
+            <v>POZO ALMONTE SOLAR 3 S.A.</v>
+          </cell>
           <cell r="D16" t="str">
             <v>PFV POZO ALMONTE SOLAR III</v>
           </cell>
@@ -609,6 +657,9 @@
           </cell>
         </row>
         <row r="17">
+          <cell r="C17" t="str">
+            <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+          </cell>
           <cell r="D17" t="str">
             <v>PFV CARRERA PINTO</v>
           </cell>
@@ -620,6 +671,9 @@
           </cell>
         </row>
         <row r="18">
+          <cell r="C18" t="str">
+            <v>JAVIERA SPA</v>
+          </cell>
           <cell r="D18" t="str">
             <v>PFV JAVIERA</v>
           </cell>
@@ -631,6 +685,9 @@
           </cell>
         </row>
         <row r="19">
+          <cell r="C19" t="str">
+            <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+          </cell>
           <cell r="D19" t="str">
             <v>PFV EL ROMERO</v>
           </cell>
@@ -642,6 +699,9 @@
           </cell>
         </row>
         <row r="20">
+          <cell r="C20" t="str">
+            <v>AMANECER SOLAR SPA</v>
+          </cell>
           <cell r="D20" t="str">
             <v>PFV LLANO DE LLAMPOS</v>
           </cell>
@@ -653,6 +713,9 @@
           </cell>
         </row>
         <row r="21">
+          <cell r="C21" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D21" t="str">
             <v>PFV LALACKAMA</v>
           </cell>
@@ -664,6 +727,9 @@
           </cell>
         </row>
         <row r="22">
+          <cell r="C22" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D22" t="str">
             <v>PFV LALACKAMA II</v>
           </cell>
@@ -675,6 +741,9 @@
           </cell>
         </row>
         <row r="23">
+          <cell r="C23" t="str">
+            <v>PLANTA SOLAR SAN PEDRO III SPA</v>
+          </cell>
           <cell r="D23" t="str">
             <v>PFV JAMA</v>
           </cell>
@@ -686,6 +755,9 @@
           </cell>
         </row>
         <row r="24">
+          <cell r="C24" t="str">
+            <v>PARQUE SOLAR FOTOVOLTAICO LUZ DEL NORTE SPA</v>
+          </cell>
           <cell r="D24" t="str">
             <v>PFV LUZ DEL NORTE</v>
           </cell>
@@ -697,6 +769,9 @@
           </cell>
         </row>
         <row r="25">
+          <cell r="C25" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D25" t="str">
             <v>PFV DON HUMBERTO</v>
           </cell>
@@ -708,6 +783,9 @@
           </cell>
         </row>
         <row r="26">
+          <cell r="C26" t="str">
+            <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+          </cell>
           <cell r="D26" t="str">
             <v>PFV PAMPA SOLAR NORTE</v>
           </cell>
@@ -719,6 +797,9 @@
           </cell>
         </row>
         <row r="27">
+          <cell r="C27" t="str">
+            <v>ENGIE ENERGÍA CHILE S.A.</v>
+          </cell>
           <cell r="D27" t="str">
             <v>PFV CAPRICORNIO</v>
           </cell>
@@ -730,6 +811,9 @@
           </cell>
         </row>
         <row r="28">
+          <cell r="C28" t="str">
+            <v>ANDES SOLAR SPA</v>
+          </cell>
           <cell r="D28" t="str">
             <v>PFV ANDES SOLAR</v>
           </cell>
@@ -741,6 +825,9 @@
           </cell>
         </row>
         <row r="29">
+          <cell r="C29" t="str">
+            <v>COPEC RENOVABLES SPA</v>
+          </cell>
           <cell r="D29" t="str">
             <v>PFV GRANJA SOLAR</v>
           </cell>
@@ -752,6 +839,9 @@
           </cell>
         </row>
         <row r="30">
+          <cell r="C30" t="str">
+            <v>SOLAR ELENA SPA</v>
+          </cell>
           <cell r="D30" t="str">
             <v>PFV ELENA</v>
           </cell>
@@ -763,6 +853,9 @@
           </cell>
         </row>
         <row r="31">
+          <cell r="C31" t="str">
+            <v>SANTIAGO SOLAR S.A.</v>
+          </cell>
           <cell r="D31" t="str">
             <v>PFV SANTIAGO SOLAR</v>
           </cell>
@@ -774,6 +867,9 @@
           </cell>
         </row>
         <row r="32">
+          <cell r="C32" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D32" t="str">
             <v>PFV FINIS TERRAE</v>
           </cell>
@@ -785,6 +881,9 @@
           </cell>
         </row>
         <row r="33">
+          <cell r="C33" t="str">
+            <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+          </cell>
           <cell r="D33" t="str">
             <v>PFV USYA</v>
           </cell>
@@ -796,6 +895,9 @@
           </cell>
         </row>
         <row r="34">
+          <cell r="C34" t="str">
+            <v>PARQUE SOLAR TANGUA SPA</v>
+          </cell>
           <cell r="D34" t="str">
             <v>PFV TUTUVEN</v>
           </cell>
@@ -807,6 +909,9 @@
           </cell>
         </row>
         <row r="35">
+          <cell r="C35" t="str">
+            <v>CONEJO SOLAR SPA</v>
+          </cell>
           <cell r="D35" t="str">
             <v>PFV CONEJO SOLAR</v>
           </cell>
@@ -818,6 +923,9 @@
           </cell>
         </row>
         <row r="36">
+          <cell r="C36" t="str">
+            <v>OPDENERGY GENERACIÓN SPA</v>
+          </cell>
           <cell r="D36" t="str">
             <v>PFV SOL DE LOS ANDES</v>
           </cell>
@@ -829,6 +937,9 @@
           </cell>
         </row>
         <row r="37">
+          <cell r="C37" t="str">
+            <v>COPIAPÓ SOLAR SPA</v>
+          </cell>
           <cell r="D37" t="str">
             <v>PFV DESIERTO DE ATACAMA</v>
           </cell>
@@ -840,6 +951,9 @@
           </cell>
         </row>
         <row r="38">
+          <cell r="C38" t="str">
+            <v>BOLERO SPA</v>
+          </cell>
           <cell r="D38" t="str">
             <v>PFV BOLERO</v>
           </cell>
@@ -851,6 +965,9 @@
           </cell>
         </row>
         <row r="39">
+          <cell r="C39" t="str">
+            <v>AELA GENERACIÓN S.A.</v>
+          </cell>
           <cell r="D39" t="str">
             <v>PFV SALVADOR</v>
           </cell>
@@ -862,6 +979,9 @@
           </cell>
         </row>
         <row r="40">
+          <cell r="C40" t="str">
+            <v>TSGF SPA</v>
+          </cell>
           <cell r="D40" t="str">
             <v>PFV SANTA ISABEL</v>
           </cell>
@@ -873,6 +993,9 @@
           </cell>
         </row>
         <row r="41">
+          <cell r="C41" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D41" t="str">
             <v>PFV GUANCHOI</v>
           </cell>
@@ -884,6 +1007,9 @@
           </cell>
         </row>
         <row r="42">
+          <cell r="C42" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D42" t="str">
             <v>PFV SOL DE LILA</v>
           </cell>
@@ -895,6 +1021,9 @@
           </cell>
         </row>
         <row r="43">
+          <cell r="C43" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D43" t="str">
             <v>PFV AZABACHE</v>
           </cell>
@@ -906,6 +1035,9 @@
           </cell>
         </row>
         <row r="44">
+          <cell r="C44" t="str">
+            <v>EL PELÍCANO SOLAR COMPANY SPA</v>
+          </cell>
           <cell r="D44" t="str">
             <v>PFV EL PELICANO</v>
           </cell>
@@ -917,6 +1049,9 @@
           </cell>
         </row>
         <row r="45">
+          <cell r="C45" t="str">
+            <v>CERRO DOMINADOR CSP S.A.</v>
+          </cell>
           <cell r="D45" t="str">
             <v>PFV CERRO DOMINADOR</v>
           </cell>
@@ -928,6 +1063,9 @@
           </cell>
         </row>
         <row r="46">
+          <cell r="C46" t="str">
+            <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
+          </cell>
           <cell r="D46" t="str">
             <v>PFV URIBE SOLAR</v>
           </cell>
@@ -939,6 +1077,9 @@
           </cell>
         </row>
         <row r="47">
+          <cell r="C47" t="str">
+            <v>AELA GENERACIÓN S.A.</v>
+          </cell>
           <cell r="D47" t="str">
             <v>PFV SAN ANDRES</v>
           </cell>
@@ -950,6 +1091,9 @@
           </cell>
         </row>
         <row r="48">
+          <cell r="C48" t="str">
+            <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
+          </cell>
           <cell r="D48" t="str">
             <v>PFV NUEVO QUILLAGUA</v>
           </cell>
@@ -961,6 +1105,9 @@
           </cell>
         </row>
         <row r="49">
+          <cell r="C49" t="str">
+            <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+          </cell>
           <cell r="D49" t="str">
             <v>PFV ALMEYDA</v>
           </cell>
@@ -972,6 +1119,9 @@
           </cell>
         </row>
         <row r="50">
+          <cell r="C50" t="str">
+            <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+          </cell>
           <cell r="D50" t="str">
             <v>PFV DOMEYKO</v>
           </cell>
@@ -983,6 +1133,9 @@
           </cell>
         </row>
         <row r="51">
+          <cell r="C51" t="str">
+            <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
+          </cell>
           <cell r="D51" t="str">
             <v>PFV NUEVO QUILLAGUA II</v>
           </cell>
@@ -994,6 +1147,9 @@
           </cell>
         </row>
         <row r="52">
+          <cell r="C52" t="str">
+            <v>CÓNDOR ENERGÍA SPA</v>
+          </cell>
           <cell r="D52" t="str">
             <v>PFV RIO ESCONDIDO</v>
           </cell>
@@ -1005,6 +1161,9 @@
           </cell>
         </row>
         <row r="53">
+          <cell r="C53" t="str">
+            <v>PARQUE SOLAR LEYDA SPA</v>
+          </cell>
           <cell r="D53" t="str">
             <v>PFV LEYDA</v>
           </cell>
@@ -1016,6 +1175,9 @@
           </cell>
         </row>
         <row r="54">
+          <cell r="C54" t="str">
+            <v>ATACAMA SOLAR SPA</v>
+          </cell>
           <cell r="D54" t="str">
             <v>PFV ATACAMA SOLAR II</v>
           </cell>
@@ -1027,6 +1189,9 @@
           </cell>
         </row>
         <row r="55">
+          <cell r="C55" t="str">
+            <v>INVERSIONES FOTOVOLTAICAS SPA</v>
+          </cell>
           <cell r="D55" t="str">
             <v>PFV WILLKA</v>
           </cell>
@@ -1038,6 +1203,9 @@
           </cell>
         </row>
         <row r="56">
+          <cell r="C56" t="str">
+            <v>SOLAR LOS LOROS SPA</v>
+          </cell>
           <cell r="D56" t="str">
             <v>PFV LOS LOROS</v>
           </cell>
@@ -1049,6 +1217,9 @@
           </cell>
         </row>
         <row r="57">
+          <cell r="C57" t="str">
+            <v>IBEREÓLICA CABO LEONES II S.A.</v>
+          </cell>
           <cell r="D57" t="str">
             <v>PFV SAN PEDRO</v>
           </cell>
@@ -1060,6 +1231,9 @@
           </cell>
         </row>
         <row r="58">
+          <cell r="C58" t="str">
+            <v>AUSTRIANSOLAR CHILE SEIS SPA</v>
+          </cell>
           <cell r="D58" t="str">
             <v>PFV LA HUELLA</v>
           </cell>
@@ -1071,6 +1245,9 @@
           </cell>
         </row>
         <row r="59">
+          <cell r="C59" t="str">
+            <v>GM HOLDINGS S.A.</v>
+          </cell>
           <cell r="D59" t="str">
             <v>PFV CEME 1</v>
           </cell>
@@ -1082,6 +1259,9 @@
           </cell>
         </row>
         <row r="60">
+          <cell r="C60" t="str">
+            <v>HUEMUL ENERGÍA SPA</v>
+          </cell>
           <cell r="D60" t="str">
             <v>PFV VALLE ESCONDIDO</v>
           </cell>
@@ -1093,6 +1273,9 @@
           </cell>
         </row>
         <row r="61">
+          <cell r="C61" t="str">
+            <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+          </cell>
           <cell r="D61" t="str">
             <v>PFV MALGARIDA</v>
           </cell>
@@ -1104,6 +1287,9 @@
           </cell>
         </row>
         <row r="62">
+          <cell r="C62" t="str">
+            <v>PARQUE SOLAR FOTOVOLTAICO SOL DEL DESIERTO SPA</v>
+          </cell>
           <cell r="D62" t="str">
             <v>PFV SOL DEL DESIERTO</v>
           </cell>
@@ -1115,6 +1301,9 @@
           </cell>
         </row>
         <row r="63">
+          <cell r="C63" t="str">
+            <v>TAMARICO SOLAR DOS SPA</v>
+          </cell>
           <cell r="D63" t="str">
             <v>PFV TAMARICO</v>
           </cell>
@@ -1126,6 +1315,9 @@
           </cell>
         </row>
         <row r="64">
+          <cell r="C64" t="str">
+            <v>AUSTRIANSOLAR CHILE CUATRO SPA</v>
+          </cell>
           <cell r="D64" t="str">
             <v>PFV HUATACONDO</v>
           </cell>
@@ -1137,6 +1329,9 @@
           </cell>
         </row>
         <row r="65">
+          <cell r="C65" t="str">
+            <v>PLANTA SOLAR TOCOPILLA SPA</v>
+          </cell>
           <cell r="D65" t="str">
             <v>PFV TAIRA</v>
           </cell>
@@ -1148,6 +1343,9 @@
           </cell>
         </row>
         <row r="66">
+          <cell r="C66" t="str">
+            <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
+          </cell>
           <cell r="D66" t="str">
             <v>PFV LA CRUZ SOLAR</v>
           </cell>
@@ -1159,6 +1357,9 @@
           </cell>
         </row>
         <row r="67">
+          <cell r="C67" t="str">
+            <v>SONNEDIX COX ENERGY CHILE SPA</v>
+          </cell>
           <cell r="D67" t="str">
             <v>PFV MESETA DE LOS ANDES</v>
           </cell>
@@ -1170,6 +1371,9 @@
           </cell>
         </row>
         <row r="68">
+          <cell r="C68" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D68" t="str">
             <v>PFV VALLE DEL SOL</v>
           </cell>
@@ -1181,6 +1385,9 @@
           </cell>
         </row>
         <row r="69">
+          <cell r="C69" t="str">
+            <v>COLBÚN S.A.</v>
+          </cell>
           <cell r="D69" t="str">
             <v>PFV DIEGO DE ALMAGRO SUR</v>
           </cell>
@@ -1192,6 +1399,9 @@
           </cell>
         </row>
         <row r="70">
+          <cell r="C70" t="str">
+            <v>HUEMUL ENERGÍA SPA</v>
+          </cell>
           <cell r="D70" t="str">
             <v>PFV PAMPA TIGRE</v>
           </cell>
@@ -1203,6 +1413,9 @@
           </cell>
         </row>
         <row r="71">
+          <cell r="C71" t="str">
+            <v>ANDES SOLAR II SPA</v>
+          </cell>
           <cell r="D71" t="str">
             <v>PFV ANDES SOLAR II-B</v>
           </cell>
@@ -1214,6 +1427,9 @@
           </cell>
         </row>
         <row r="72">
+          <cell r="C72" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D72" t="str">
             <v>PFV LAS SALINAS</v>
           </cell>
@@ -1225,6 +1441,9 @@
           </cell>
         </row>
         <row r="73">
+          <cell r="C73" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D73" t="str">
             <v>PFV CAMPOS DEL SOL</v>
           </cell>
@@ -1236,6 +1455,9 @@
           </cell>
         </row>
         <row r="74">
+          <cell r="C74" t="str">
+            <v>ENLASA GENERACIÓN CHILE S.A.</v>
+          </cell>
           <cell r="D74" t="str">
             <v>PFV CHERCAN SOLAR</v>
           </cell>
@@ -1247,6 +1469,9 @@
           </cell>
         </row>
         <row r="75">
+          <cell r="C75" t="str">
+            <v>ENGIE ENERGÍA CHILE S.A.</v>
+          </cell>
           <cell r="D75" t="str">
             <v>PFV COYA</v>
           </cell>
@@ -1258,6 +1483,9 @@
           </cell>
         </row>
         <row r="76">
+          <cell r="C76" t="str">
+            <v>ENEL GREEN POWER CHILE S.A.</v>
+          </cell>
           <cell r="D76" t="str">
             <v>PFV MANZANO</v>
           </cell>
@@ -1269,6 +1497,9 @@
           </cell>
         </row>
         <row r="77">
+          <cell r="C77" t="str">
+            <v>ANDES SOLAR IV SPA</v>
+          </cell>
           <cell r="D77" t="str">
             <v>PFV ANDES SOLAR IV</v>
           </cell>
@@ -1280,6 +1511,9 @@
           </cell>
         </row>
         <row r="78">
+          <cell r="C78" t="str">
+            <v>GR LIUN SPA</v>
+          </cell>
           <cell r="D78" t="str">
             <v>PFV TAMANGO</v>
           </cell>
@@ -1296,7 +1530,496 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
+      <sheetData sheetId="6">
+        <row r="28">
+          <cell r="A28" t="str">
+            <v>PFV DOÑA ANTONIA</v>
+          </cell>
+          <cell r="M28">
+            <v>37</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="A29" t="str">
+            <v>PFV MARIA ELENA</v>
+          </cell>
+          <cell r="M29">
+            <v>36</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="A30" t="str">
+            <v>PFV SANTA ISABEL</v>
+          </cell>
+          <cell r="M30">
+            <v>33</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="A31" t="str">
+            <v>PFV ALMEYDA</v>
+          </cell>
+          <cell r="M31">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="A32" t="str">
+            <v>PFV LUZ DEL NORTE</v>
+          </cell>
+          <cell r="M32">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="A33" t="str">
+            <v>PFV DIEGO DE ALMAGRO</v>
+          </cell>
+          <cell r="M33">
+            <v>31</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="A34" t="str">
+            <v>PFV LA HUAYCA II</v>
+          </cell>
+          <cell r="M34">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="A35" t="str">
+            <v>PFV JAMA</v>
+          </cell>
+          <cell r="M35">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="A36" t="str">
+            <v>PFV BOLERO</v>
+          </cell>
+          <cell r="M36">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="A37" t="str">
+            <v>PFV CAPRICORNIO</v>
+          </cell>
+          <cell r="M37">
+            <v>29</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="A38" t="str">
+            <v>PFV VALLE ESCONDIDO</v>
+          </cell>
+          <cell r="M38">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="A39" t="str">
+            <v>PFV CHAÑARES</v>
+          </cell>
+          <cell r="M39">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="A40" t="str">
+            <v>PFV URIBE SOLAR</v>
+          </cell>
+          <cell r="M40">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="A41" t="str">
+            <v>PFV CARRERA PINTO</v>
+          </cell>
+          <cell r="M41">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="A42" t="str">
+            <v>PFV LOS LOROS</v>
+          </cell>
+          <cell r="M42">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="A43" t="str">
+            <v>PFV EL ROMERO</v>
+          </cell>
+          <cell r="M43">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="A44" t="str">
+            <v>PFV USYA</v>
+          </cell>
+          <cell r="M44">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="A45" t="str">
+            <v>PFV DON HUMBERTO</v>
+          </cell>
+          <cell r="M45">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="A46" t="str">
+            <v>PFV TAMARICO</v>
+          </cell>
+          <cell r="M46">
+            <v>28</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="A47" t="str">
+            <v>PFV ANDES SOLAR II</v>
+          </cell>
+          <cell r="M47">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="A48" t="str">
+            <v>PFV ATACAMA SOLAR II</v>
+          </cell>
+          <cell r="M48">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="A49" t="str">
+            <v>PFV TAMAYA SOLAR</v>
+          </cell>
+          <cell r="M49">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="A50" t="str">
+            <v>PFV SALVADOR</v>
+          </cell>
+          <cell r="M50">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="A51" t="str">
+            <v>PFV TAMANGO</v>
+          </cell>
+          <cell r="M51">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="A52" t="str">
+            <v>PFV DOÑA CARMEN SOLAR</v>
+          </cell>
+          <cell r="M52">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="A53" t="str">
+            <v>PFV LEYDA</v>
+          </cell>
+          <cell r="M53">
+            <v>27</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="A54" t="str">
+            <v>PFV RIO ESCONDIDO</v>
+          </cell>
+          <cell r="M54">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="A55" t="str">
+            <v>PFV VALLE DEL SOL</v>
+          </cell>
+          <cell r="M55">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="A56" t="str">
+            <v>PFV EL PELICANO</v>
+          </cell>
+          <cell r="M56">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="A57" t="str">
+            <v>PFV GRANJA SOLAR</v>
+          </cell>
+          <cell r="M57">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="A58" t="str">
+            <v>PFV MANZANO</v>
+          </cell>
+          <cell r="M58">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="A59" t="str">
+            <v>PFV GRAN TENO</v>
+          </cell>
+          <cell r="M59">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="A60" t="str">
+            <v>PFV SAN ANDRES</v>
+          </cell>
+          <cell r="M60">
+            <v>26</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="A61" t="str">
+            <v>PFV WILLKA</v>
+          </cell>
+          <cell r="M61">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="A62" t="str">
+            <v>PFV HUATACONDO</v>
+          </cell>
+          <cell r="M62">
+            <v>25</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="A63" t="str">
+            <v>PFV SOL DE LILA</v>
+          </cell>
+          <cell r="M63">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="A64" t="str">
+            <v>PFV ELENA</v>
+          </cell>
+          <cell r="M64">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="A65" t="str">
+            <v>PFV LLANO DE LLAMPOS</v>
+          </cell>
+          <cell r="M65">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="66">
+          <cell r="A66" t="str">
+            <v>PFV ANDES SOLAR</v>
+          </cell>
+          <cell r="M66">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="67">
+          <cell r="A67" t="str">
+            <v>PFV JAVIERA</v>
+          </cell>
+          <cell r="M67">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="68">
+          <cell r="A68" t="str">
+            <v>PFV SOL DE LOS ANDES</v>
+          </cell>
+          <cell r="M68">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="69">
+          <cell r="A69" t="str">
+            <v>PFV COYA</v>
+          </cell>
+          <cell r="M69">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="70">
+          <cell r="A70" t="str">
+            <v>PFV SANTIAGO SOLAR</v>
+          </cell>
+          <cell r="M70">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="71">
+          <cell r="A71" t="str">
+            <v>PFV QUILAPILUN</v>
+          </cell>
+          <cell r="M71">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="72">
+          <cell r="A72" t="str">
+            <v>PFV LAS SALINAS</v>
+          </cell>
+          <cell r="M72">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="73">
+          <cell r="A73" t="str">
+            <v>PFV SAN PEDRO</v>
+          </cell>
+          <cell r="M73">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="74">
+          <cell r="A74" t="str">
+            <v>PFV AZABACHE</v>
+          </cell>
+          <cell r="M74">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="75">
+          <cell r="A75" t="str">
+            <v>PFV NUEVO QUILLAGUA II</v>
+          </cell>
+          <cell r="M75">
+            <v>22</v>
+          </cell>
+        </row>
+        <row r="76">
+          <cell r="A76" t="str">
+            <v>PFV CERRO DOMINADOR</v>
+          </cell>
+          <cell r="M76">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="77">
+          <cell r="A77" t="str">
+            <v>PFV ANDES SOLAR II-B</v>
+          </cell>
+          <cell r="M77">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="78">
+          <cell r="A78" t="str">
+            <v>PFV LALACKAMA</v>
+          </cell>
+          <cell r="M78">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="79">
+          <cell r="A79" t="str">
+            <v>PFV LA HUELLA</v>
+          </cell>
+          <cell r="M79">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="80">
+          <cell r="A80" t="str">
+            <v>PFV PAMPA SOLAR NORTE</v>
+          </cell>
+          <cell r="M80">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="81">
+          <cell r="A81" t="str">
+            <v>PFV MESETA DE LOS ANDES</v>
+          </cell>
+          <cell r="M81">
+            <v>21</v>
+          </cell>
+        </row>
+        <row r="82">
+          <cell r="A82" t="str">
+            <v>PFV ANDES SOLAR IV</v>
+          </cell>
+          <cell r="M82">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="83">
+          <cell r="A83" t="str">
+            <v>PFV LA CRUZ SOLAR</v>
+          </cell>
+          <cell r="M83">
+            <v>20</v>
+          </cell>
+        </row>
+        <row r="84">
+          <cell r="A84" t="str">
+            <v>PFV PAMPA TIGRE</v>
+          </cell>
+          <cell r="M84">
+            <v>19</v>
+          </cell>
+        </row>
+        <row r="85">
+          <cell r="A85" t="str">
+            <v>PFV CONEJO SOLAR</v>
+          </cell>
+          <cell r="M85">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="86">
+          <cell r="A86" t="str">
+            <v>PFV NUEVO QUILLAGUA</v>
+          </cell>
+          <cell r="M86">
+            <v>18</v>
+          </cell>
+        </row>
+        <row r="87">
+          <cell r="A87" t="str">
+            <v>PFV ANDES SOLAR III</v>
+          </cell>
+          <cell r="M87">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="88">
+          <cell r="A88" t="str">
+            <v>PFV VICTOR JARA</v>
+          </cell>
+          <cell r="M88">
+            <v>10</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="7">
         <row r="30">
           <cell r="A30" t="str">
@@ -15238,10 +15961,6 @@
     </sheetDataSet>
   </externalBook>
 </externalLink>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -15510,1557 +16229,2053 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:H62"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" customWidth="1"/>
-    <col min="3" max="4" width="16.21875" customWidth="1"/>
-    <col min="5" max="5" width="13" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5703125" customWidth="1"/>
+    <col min="4" max="4" width="14.5703125" customWidth="1"/>
+    <col min="5" max="6" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
-      <c r="B2">
+      <c r="B2" t="str">
+        <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>GR CHAÑAR SPA</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.XLOOKUP(A2,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>10</v>
+      </c>
+      <c r="D2">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="C2" s="4" t="str">
+      <c r="E2" s="4" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="D2" s="6" t="str">
+      <c r="F2" s="6" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="E2" t="str">
+      <c r="G2" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
-      <c r="B3">
+      <c r="B3" t="str">
+        <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ANDES SOLAR III SPA</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.XLOOKUP(A3,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>10</v>
+      </c>
+      <c r="D3">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="str">
+      <c r="E3" s="4" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="D3" s="6" t="str">
+      <c r="F3" s="6" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="E3" t="str">
+      <c r="G3" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>53</v>
       </c>
-      <c r="B4">
+      <c r="B4" t="str">
+        <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>GR ALGARROBO SPA</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.XLOOKUP(A4,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="C4" s="4">
+      <c r="E4" s="4">
         <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>340.36306314953293</v>
       </c>
-      <c r="D4" s="6">
+      <c r="F4" s="6">
         <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>340.36306314953293</v>
       </c>
-      <c r="E4">
+      <c r="G4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F4">
+      <c r="H4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
-      <c r="B5">
+      <c r="B5" t="str">
+        <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ANDES SOLAR II SPA</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.XLOOKUP(A5,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C5" s="4">
+      <c r="E5" s="4">
         <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>261.63933396239332</v>
       </c>
-      <c r="D5" s="6">
+      <c r="F5" s="6">
         <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>154.25090610149064</v>
       </c>
-      <c r="E5">
+      <c r="G5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F5">
+      <c r="H5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
-      <c r="B6">
+      <c r="B6" t="str">
+        <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENGIE ENERGÍA CHILE S.A.</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.XLOOKUP(A6,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C6" s="4">
+      <c r="E6" s="4">
         <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>258.53120988875185</v>
       </c>
-      <c r="D6" s="6">
+      <c r="F6" s="6">
         <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>116.69232684199737</v>
       </c>
-      <c r="E6">
+      <c r="G6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F6">
+      <c r="H6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
-      <c r="B7">
+      <c r="B7" t="str">
+        <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>DOÑA ANTONIA SOLAR SPA</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.XLOOKUP(A7,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>37</v>
+      </c>
+      <c r="D7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>37</v>
       </c>
-      <c r="C7" s="4">
+      <c r="E7" s="4">
         <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>225.14796721950631</v>
       </c>
-      <c r="D7" s="6">
+      <c r="F7" s="6">
         <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>225.14796721950631</v>
       </c>
-      <c r="E7">
+      <c r="G7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F7">
+      <c r="H7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
-      <c r="B8">
+      <c r="B8" t="str">
+        <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.XLOOKUP(A8,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>31</v>
+      </c>
+      <c r="D8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="C8" s="4">
+      <c r="E8" s="4">
         <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>212.91676434569115</v>
       </c>
-      <c r="D8" s="6">
+      <c r="F8" s="6">
         <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>190.90031470068843</v>
       </c>
-      <c r="E8">
+      <c r="G8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F8">
+      <c r="H8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
-      <c r="B9">
+      <c r="B9" t="str">
+        <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENERGÍA CERRO EL MORADO S.A.</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.XLOOKUP(A9,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C9" s="4">
+      <c r="E9" s="4">
         <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>184.07262385643253</v>
       </c>
-      <c r="D9" s="6">
+      <c r="F9" s="6">
         <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>173.34955912683731</v>
       </c>
-      <c r="E9">
+      <c r="G9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F9">
+      <c r="H9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
-      <c r="B10">
+      <c r="B10" t="str">
+        <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENLIGHT INVESTMENTS SPA</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.XLOOKUP(A10,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>30</v>
+      </c>
+      <c r="D10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>31</v>
       </c>
-      <c r="C10" s="4">
+      <c r="E10" s="4">
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>182.41667069729561</v>
       </c>
-      <c r="D10" s="6">
+      <c r="F10" s="6">
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>145.62272360314196</v>
       </c>
-      <c r="E10">
+      <c r="G10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F10">
+      <c r="H10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
-      <c r="B11">
+      <c r="B11" t="str">
+        <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C11">
+        <f>_xlfn.XLOOKUP(A11,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="C11" s="4">
+      <c r="E11" s="4">
         <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>178.3717745686545</v>
       </c>
-      <c r="D11" s="6">
+      <c r="F11" s="6">
         <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>160.32307404988748</v>
       </c>
-      <c r="E11">
+      <c r="G11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="F11">
+      <c r="H11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
-      <c r="B12">
+      <c r="B12" t="str">
+        <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>GENERACIÓN SOLAR SPA</v>
+      </c>
+      <c r="C12">
+        <f>_xlfn.XLOOKUP(A12,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>36</v>
+      </c>
+      <c r="D12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="C12" s="4">
+      <c r="E12" s="4">
         <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>165.40925469740816</v>
       </c>
-      <c r="D12" s="6">
+      <c r="F12" s="6">
         <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>164.3939197409471</v>
       </c>
-      <c r="E12">
+      <c r="G12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F12">
+      <c r="H12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
-      <c r="B13">
+      <c r="B13" t="str">
+        <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>CHUNGUNGO S.A.</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.XLOOKUP(A13,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C13" s="4">
+      <c r="E13" s="4">
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>159.96688852477408</v>
       </c>
-      <c r="D13" s="6">
+      <c r="F13" s="6">
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>150.66054694362239</v>
       </c>
-      <c r="E13">
+      <c r="G13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F13">
+      <c r="H13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
-      <c r="B14">
+      <c r="B14" t="str">
+        <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.XLOOKUP(A14,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C14" s="4">
+      <c r="E14" s="4">
         <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>155.50186037465843</v>
       </c>
-      <c r="D14" s="6">
+      <c r="F14" s="6">
         <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>131.2541894992178</v>
       </c>
-      <c r="E14">
+      <c r="G14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F14">
+      <c r="H14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
-      <c r="B15">
+      <c r="B15" t="str">
+        <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>JAVIERA SPA</v>
+      </c>
+      <c r="C15">
+        <f>_xlfn.XLOOKUP(A15,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C15" s="4">
+      <c r="E15" s="4">
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>151.54931562087606</v>
       </c>
-      <c r="D15" s="6">
+      <c r="F15" s="6">
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>153.36115611189666</v>
       </c>
-      <c r="E15">
+      <c r="G15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F15">
+      <c r="H15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
-      <c r="B16">
+      <c r="B16" t="str">
+        <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+      </c>
+      <c r="C16">
+        <f>_xlfn.XLOOKUP(A16,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C16" s="4">
+      <c r="E16" s="4">
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>150.53150087405055</v>
       </c>
-      <c r="D16" s="6">
+      <c r="F16" s="6">
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>126.29025312310564</v>
       </c>
-      <c r="E16">
+      <c r="G16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F16">
+      <c r="H16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
-      <c r="B17">
+      <c r="B17" t="str">
+        <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>AMANECER SOLAR SPA</v>
+      </c>
+      <c r="C17">
+        <f>_xlfn.XLOOKUP(A17,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>24</v>
+      </c>
+      <c r="D17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C17" s="4">
+      <c r="E17" s="4">
         <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>147.10751532332384</v>
       </c>
-      <c r="D17" s="6">
+      <c r="F17" s="6">
         <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>142.61474714826912</v>
       </c>
-      <c r="E17">
+      <c r="G17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="F17">
+      <c r="H17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
-      <c r="B18">
+      <c r="B18" t="str">
+        <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C18">
+        <f>_xlfn.XLOOKUP(A18,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="C18" s="4">
+      <c r="E18" s="4">
         <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>143.37493574349742</v>
       </c>
-      <c r="D18" s="6">
+      <c r="F18" s="6">
         <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>133.7946701446663</v>
       </c>
-      <c r="E18">
+      <c r="G18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F18">
+      <c r="H18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
-      <c r="B19">
+      <c r="B19" t="str">
+        <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>PLANTA SOLAR SAN PEDRO III SPA</v>
+      </c>
+      <c r="C19">
+        <f>_xlfn.XLOOKUP(A19,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>29</v>
+      </c>
+      <c r="D19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C19" s="4">
+      <c r="E19" s="4">
         <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>137.30925624718762</v>
       </c>
-      <c r="D19" s="6">
+      <c r="F19" s="6">
         <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>123.4689482698556</v>
       </c>
-      <c r="E19">
+      <c r="G19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F19">
+      <c r="H19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
-      <c r="B20">
+      <c r="B20" t="str">
+        <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>PARQUE SOLAR FOTOVOLTAICO LUZ DEL NORTE SPA</v>
+      </c>
+      <c r="C20">
+        <f>_xlfn.XLOOKUP(A20,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>31</v>
+      </c>
+      <c r="D20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="C20" s="4">
+      <c r="E20" s="4">
         <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>134.08829640288874</v>
       </c>
-      <c r="D20" s="6">
+      <c r="F20" s="6">
         <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>118.82812570112476</v>
       </c>
-      <c r="E20">
+      <c r="G20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F20">
+      <c r="H20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>57</v>
       </c>
-      <c r="B21">
+      <c r="B21" t="str">
+        <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C21">
+        <f>_xlfn.XLOOKUP(A21,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="C21" s="4">
+      <c r="E21" s="4">
         <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>130.48572110243344</v>
       </c>
-      <c r="D21" s="6">
+      <c r="F21" s="6">
         <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>130.48572110243344</v>
       </c>
-      <c r="E21">
+      <c r="G21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F21">
+      <c r="H21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
-      <c r="B22">
+      <c r="B22" t="str">
+        <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
+      </c>
+      <c r="C22">
+        <f>_xlfn.XLOOKUP(A22,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C22" s="4">
+      <c r="E22" s="4">
         <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>127.45927135686706</v>
       </c>
-      <c r="D22" s="6">
+      <c r="F22" s="6">
         <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>117.55952975574159</v>
       </c>
-      <c r="E22">
+      <c r="G22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F22">
+      <c r="H22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
-      <c r="B23">
+      <c r="B23" t="str">
+        <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENGIE ENERGÍA CHILE S.A.</v>
+      </c>
+      <c r="C23">
+        <f>_xlfn.XLOOKUP(A23,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>29</v>
+      </c>
+      <c r="D23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="C23" s="4">
+      <c r="E23" s="4">
         <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>120.86019668952748</v>
       </c>
-      <c r="D23" s="6">
+      <c r="F23" s="6">
         <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>77.673577614814533</v>
       </c>
-      <c r="E23">
+      <c r="G23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="F23">
+      <c r="H23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
-      <c r="B24">
+      <c r="B24" t="str">
+        <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ANDES SOLAR SPA</v>
+      </c>
+      <c r="C24">
+        <f>_xlfn.XLOOKUP(A24,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="C24" s="4">
+      <c r="E24" s="4">
         <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>117.00468059513956</v>
       </c>
-      <c r="D24" s="6">
+      <c r="F24" s="6">
         <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>107.06022465930636</v>
       </c>
-      <c r="E24">
+      <c r="G24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="F24">
+      <c r="H24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="B25">
+      <c r="B25" t="str">
+        <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>COPEC RENOVABLES SPA</v>
+      </c>
+      <c r="C25">
+        <f>_xlfn.XLOOKUP(A25,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C25" s="4">
+      <c r="E25" s="4">
         <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>115.95328370578751</v>
       </c>
-      <c r="D25" s="6">
+      <c r="F25" s="6">
         <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>73.249911595920381</v>
       </c>
-      <c r="E25">
+      <c r="G25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="F25">
+      <c r="H25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>47</v>
       </c>
-      <c r="B26">
+      <c r="B26" t="str">
+        <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>SOLAR ELENA SPA</v>
+      </c>
+      <c r="C26">
+        <f>_xlfn.XLOOKUP(A26,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>24</v>
+      </c>
+      <c r="D26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C26" s="4">
+      <c r="E26" s="4">
         <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>113.47776926480164</v>
       </c>
-      <c r="D26" s="6">
+      <c r="F26" s="6">
         <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>77.517731576601136</v>
       </c>
-      <c r="E26">
+      <c r="G26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="F26">
+      <c r="H26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
-      <c r="B27">
+      <c r="B27" t="str">
+        <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>SANTIAGO SOLAR S.A.</v>
+      </c>
+      <c r="C27">
+        <f>_xlfn.XLOOKUP(A27,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C27" s="4">
+      <c r="E27" s="4">
         <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>106.19134821796176</v>
       </c>
-      <c r="D27" s="6">
+      <c r="F27" s="6">
         <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>106.46671004953231</v>
       </c>
-      <c r="E27">
+      <c r="G27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="F27">
+      <c r="H27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
-      <c r="B28">
+      <c r="B28" t="str">
+        <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+      </c>
+      <c r="C28">
+        <f>_xlfn.XLOOKUP(A28,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C28" s="4">
+      <c r="E28" s="4">
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>101.99069847540675</v>
       </c>
-      <c r="D28" s="6">
+      <c r="F28" s="6">
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>71.964555409210689</v>
       </c>
-      <c r="E28">
+      <c r="G28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="F28">
+      <c r="H28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
-      <c r="B29">
+      <c r="B29" t="str">
+        <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>CONEJO SOLAR SPA</v>
+      </c>
+      <c r="C29">
+        <f>_xlfn.XLOOKUP(A29,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>18</v>
+      </c>
+      <c r="D29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="C29" s="4">
+      <c r="E29" s="4">
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>97.844422713934776</v>
       </c>
-      <c r="D29" s="6">
+      <c r="F29" s="6">
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>97.238183111387499</v>
       </c>
-      <c r="E29">
+      <c r="G29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="F29">
+      <c r="H29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
-      <c r="B30">
+      <c r="B30" t="str">
+        <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>OPDENERGY GENERACIÓN SPA</v>
+      </c>
+      <c r="C30">
+        <f>_xlfn.XLOOKUP(A30,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="C30" s="4">
+      <c r="E30" s="4">
         <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>96.151671241546708</v>
       </c>
-      <c r="D30" s="6">
+      <c r="F30" s="6">
         <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>63.301005566807682</v>
       </c>
-      <c r="E30">
+      <c r="G30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="F30">
+      <c r="H30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>22</v>
       </c>
-      <c r="B31">
+      <c r="B31" t="str">
+        <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>BOLERO SPA</v>
+      </c>
+      <c r="C31">
+        <f>_xlfn.XLOOKUP(A31,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>29</v>
+      </c>
+      <c r="D31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C31" s="4">
+      <c r="E31" s="4">
         <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>95.498581478081192</v>
       </c>
-      <c r="D31" s="6">
+      <c r="F31" s="6">
         <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>91.571363913723303</v>
       </c>
-      <c r="E31">
+      <c r="G31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="F31">
+      <c r="H31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
-      <c r="B32">
+      <c r="B32" t="str">
+        <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>AELA GENERACIÓN S.A.</v>
+      </c>
+      <c r="C32">
+        <f>_xlfn.XLOOKUP(A32,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="C32" s="4">
+      <c r="E32" s="4">
         <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>93.607486248881401</v>
       </c>
-      <c r="D32" s="6">
+      <c r="F32" s="6">
         <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>279.63938708891095</v>
       </c>
-      <c r="E32">
+      <c r="G32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="F32">
+      <c r="H32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
-      <c r="B33">
+      <c r="B33" t="str">
+        <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>TSGF SPA</v>
+      </c>
+      <c r="C33">
+        <f>_xlfn.XLOOKUP(A33,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>33</v>
+      </c>
+      <c r="D33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="C33" s="4">
+      <c r="E33" s="4">
         <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>92.990504377886353</v>
       </c>
-      <c r="D33" s="6">
+      <c r="F33" s="6">
         <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>137.26143535275247</v>
       </c>
-      <c r="E33">
+      <c r="G33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="F33">
+      <c r="H33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
-      <c r="B34">
+      <c r="B34" t="str">
+        <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C34">
+        <f>_xlfn.XLOOKUP(A34,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>24</v>
+      </c>
+      <c r="D34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C34" s="4">
+      <c r="E34" s="4">
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>91.398662501573469</v>
       </c>
-      <c r="D34" s="6">
+      <c r="F34" s="6">
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.595599722111082</v>
       </c>
-      <c r="E34">
+      <c r="G34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F34">
+      <c r="H34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
-      <c r="B35">
+      <c r="B35" t="str">
+        <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C35">
+        <f>_xlfn.XLOOKUP(A35,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>22</v>
+      </c>
+      <c r="D35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C35" s="4">
+      <c r="E35" s="4">
         <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>90.663901448570243</v>
       </c>
-      <c r="D35" s="6">
+      <c r="F35" s="6">
         <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.308560240126781</v>
       </c>
-      <c r="E35">
+      <c r="G35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F35">
+      <c r="H35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>20</v>
       </c>
-      <c r="B36">
+      <c r="B36" t="str">
+        <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>EL PELÍCANO SOLAR COMPANY SPA</v>
+      </c>
+      <c r="C36">
+        <f>_xlfn.XLOOKUP(A36,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C36" s="4">
+      <c r="E36" s="4">
         <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>87.353465167615525</v>
       </c>
-      <c r="D36" s="6">
+      <c r="F36" s="6">
         <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>85.46269087234684</v>
       </c>
-      <c r="E36">
+      <c r="G36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F36">
+      <c r="H36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>23</v>
       </c>
-      <c r="B37">
+      <c r="B37" t="str">
+        <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>CERRO DOMINADOR CSP S.A.</v>
+      </c>
+      <c r="C37">
+        <f>_xlfn.XLOOKUP(A37,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>17</v>
       </c>
-      <c r="C37" s="4">
+      <c r="E37" s="4">
         <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>81.329008645014241</v>
       </c>
-      <c r="D37" s="6">
+      <c r="F37" s="6">
         <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>78.097831211286106</v>
       </c>
-      <c r="E37">
+      <c r="G37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F37">
+      <c r="H37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
-      <c r="B38">
+      <c r="B38" t="str">
+        <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
+      </c>
+      <c r="C38">
+        <f>_xlfn.XLOOKUP(A38,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C38" s="4">
+      <c r="E38" s="4">
         <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>77.489457860750406</v>
       </c>
-      <c r="D38" s="6">
+      <c r="F38" s="6">
         <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>96.082038641272788</v>
       </c>
-      <c r="E38">
+      <c r="G38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F38">
+      <c r="H38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1</v>
       </c>
-      <c r="B39">
+      <c r="B39" t="str">
+        <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>AELA GENERACIÓN S.A.</v>
+      </c>
+      <c r="C39">
+        <f>_xlfn.XLOOKUP(A39,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C39" s="4">
+      <c r="E39" s="4">
         <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>76.428287381574279</v>
       </c>
-      <c r="D39" s="6">
+      <c r="F39" s="6">
         <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>213.69474255136006</v>
       </c>
-      <c r="E39">
+      <c r="G39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F39">
+      <c r="H39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
-      <c r="B40">
+      <c r="B40" t="str">
+        <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
+      </c>
+      <c r="C40">
+        <f>_xlfn.XLOOKUP(A40,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>18</v>
+      </c>
+      <c r="D40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="C40" s="4">
+      <c r="E40" s="4">
         <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>74.352491824072459</v>
       </c>
-      <c r="D40" s="6">
+      <c r="F40" s="6">
         <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>62.959486745461732</v>
       </c>
-      <c r="E40">
+      <c r="G40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F40">
+      <c r="H40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>25</v>
       </c>
-      <c r="B41">
+      <c r="B41" t="str">
+        <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
+      </c>
+      <c r="C41">
+        <f>_xlfn.XLOOKUP(A41,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>31</v>
+      </c>
+      <c r="D41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C41" s="4">
+      <c r="E41" s="4">
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>72.185778981537624</v>
       </c>
-      <c r="D41" s="6">
+      <c r="F41" s="6">
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>56.377157688509307</v>
       </c>
-      <c r="E41">
+      <c r="G41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="F41">
+      <c r="H41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
-      <c r="B42">
+      <c r="B42" t="str">
+        <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
+      </c>
+      <c r="C42">
+        <f>_xlfn.XLOOKUP(A42,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>22</v>
+      </c>
+      <c r="D42">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C42" s="4">
+      <c r="E42" s="4">
         <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>63.442273740022721</v>
       </c>
-      <c r="D42" s="6" t="str">
+      <c r="F42" s="6" t="str">
         <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="E42">
+      <c r="G42">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F42" t="str">
+      <c r="H42" t="str">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
-      <c r="B43">
+      <c r="B43" t="str">
+        <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>CÓNDOR ENERGÍA SPA</v>
+      </c>
+      <c r="C43">
+        <f>_xlfn.XLOOKUP(A43,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C43" s="4">
+      <c r="E43" s="4">
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>63.352321353673524</v>
       </c>
-      <c r="D43" s="6">
+      <c r="F43" s="6">
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.213209897553845</v>
       </c>
-      <c r="E43">
+      <c r="G43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F43">
+      <c r="H43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
-      <c r="B44">
+      <c r="B44" t="str">
+        <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>PARQUE SOLAR LEYDA SPA</v>
+      </c>
+      <c r="C44">
+        <f>_xlfn.XLOOKUP(A44,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C44" s="4">
+      <c r="E44" s="4">
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>62.577762755201285</v>
       </c>
-      <c r="D44" s="6" t="str">
+      <c r="F44" s="6" t="str">
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="E44">
+      <c r="G44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F44" t="str">
+      <c r="H44" t="str">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>31</v>
       </c>
-      <c r="B45">
+      <c r="B45" t="str">
+        <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ATACAMA SOLAR SPA</v>
+      </c>
+      <c r="C45">
+        <f>_xlfn.XLOOKUP(A45,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C45" s="4">
+      <c r="E45" s="4">
         <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>62.216151585762177</v>
       </c>
-      <c r="D45" s="6">
+      <c r="F45" s="6">
         <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>51.173475954890485</v>
       </c>
-      <c r="E45">
+      <c r="G45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F45">
+      <c r="H45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
-      <c r="B46">
+      <c r="B46" t="str">
+        <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>INVERSIONES FOTOVOLTAICAS SPA</v>
+      </c>
+      <c r="C46">
+        <f>_xlfn.XLOOKUP(A46,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>25</v>
+      </c>
+      <c r="D46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C46" s="4">
+      <c r="E46" s="4">
         <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>60.129708168778912</v>
       </c>
-      <c r="D46" s="6">
+      <c r="F46" s="6">
         <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>60.129708168778912</v>
       </c>
-      <c r="E46">
+      <c r="G46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F46">
+      <c r="H46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>11</v>
       </c>
-      <c r="B47">
+      <c r="B47" t="str">
+        <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>SOLAR LOS LOROS SPA</v>
+      </c>
+      <c r="C47">
+        <f>_xlfn.XLOOKUP(A47,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="C47" s="4">
+      <c r="E47" s="4">
         <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>58.793466696212718</v>
       </c>
-      <c r="D47" s="6">
+      <c r="F47" s="6">
         <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>98.698739826924182</v>
       </c>
-      <c r="E47">
+      <c r="G47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="F47">
+      <c r="H47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
       </c>
-      <c r="B48">
+      <c r="B48" t="str">
+        <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>IBEREÓLICA CABO LEONES II S.A.</v>
+      </c>
+      <c r="C48">
+        <f>_xlfn.XLOOKUP(A48,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>22</v>
+      </c>
+      <c r="D48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C48" s="4">
+      <c r="E48" s="4">
         <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>56.184687451190754</v>
       </c>
-      <c r="D48" s="6">
+      <c r="F48" s="6">
         <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>51.658946411605257</v>
       </c>
-      <c r="E48">
+      <c r="G48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="F48">
+      <c r="H48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
-      <c r="B49">
+      <c r="B49" t="str">
+        <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>AUSTRIANSOLAR CHILE SEIS SPA</v>
+      </c>
+      <c r="C49">
+        <f>_xlfn.XLOOKUP(A49,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="C49" s="4">
+      <c r="E49" s="4">
         <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>56.144466313767701</v>
       </c>
-      <c r="D49" s="6">
+      <c r="F49" s="6">
         <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>53.422824583531359</v>
       </c>
-      <c r="E49">
+      <c r="G49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="F49">
+      <c r="H49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>40</v>
       </c>
-      <c r="B50">
+      <c r="B50" t="str">
+        <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>HUEMUL ENERGÍA SPA</v>
+      </c>
+      <c r="C50">
+        <f>_xlfn.XLOOKUP(A50,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="C50" s="4">
+      <c r="E50" s="4">
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>53.365144868727548</v>
       </c>
-      <c r="D50" s="6">
+      <c r="F50" s="6">
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>48.561374555411653</v>
       </c>
-      <c r="E50">
+      <c r="G50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="F50">
+      <c r="H50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
-      <c r="B51">
+      <c r="B51" t="str">
+        <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>TAMARICO SOLAR DOS SPA</v>
+      </c>
+      <c r="C51">
+        <f>_xlfn.XLOOKUP(A51,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>28</v>
+      </c>
+      <c r="D51">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="C51" s="4">
+      <c r="E51" s="4">
         <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>51.529372024830337</v>
       </c>
-      <c r="D51" s="6" t="str">
+      <c r="F51" s="6" t="str">
         <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="E51">
+      <c r="G51">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="F51" t="str">
+      <c r="H51" t="str">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
-      <c r="B52">
+      <c r="B52" t="str">
+        <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>AUSTRIANSOLAR CHILE CUATRO SPA</v>
+      </c>
+      <c r="C52">
+        <f>_xlfn.XLOOKUP(A52,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>25</v>
+      </c>
+      <c r="D52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="C52" s="4">
+      <c r="E52" s="4">
         <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>50.304776192582921</v>
       </c>
-      <c r="D52" s="6">
+      <c r="F52" s="6">
         <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>60.987509864450338</v>
       </c>
-      <c r="E52">
+      <c r="G52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="F52">
+      <c r="H52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>37</v>
       </c>
-      <c r="B53">
+      <c r="B53" t="str">
+        <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
+      </c>
+      <c r="C53">
+        <f>_xlfn.XLOOKUP(A53,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>20</v>
+      </c>
+      <c r="D53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="C53" s="4">
+      <c r="E53" s="4">
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>47.267385112566615</v>
       </c>
-      <c r="D53" s="6">
+      <c r="F53" s="6">
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>43.797716855137359</v>
       </c>
-      <c r="E53">
+      <c r="G53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="F53">
+      <c r="H53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
-      <c r="B54">
+      <c r="B54" t="str">
+        <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>SONNEDIX COX ENERGY CHILE SPA</v>
+      </c>
+      <c r="C54">
+        <f>_xlfn.XLOOKUP(A54,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C54" s="4">
+      <c r="E54" s="4">
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>46.921269641603153</v>
       </c>
-      <c r="D54" s="6">
+      <c r="F54" s="6">
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>53.406650841276864</v>
       </c>
-      <c r="E54">
+      <c r="G54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="F54">
+      <c r="H54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>43</v>
       </c>
-      <c r="B55">
+      <c r="B55" t="str">
+        <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C55">
+        <f>_xlfn.XLOOKUP(A55,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="C55" s="4">
+      <c r="E55" s="4">
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>46.780683612984056</v>
       </c>
-      <c r="D55" s="6">
+      <c r="F55" s="6">
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>45.575537933172924</v>
       </c>
-      <c r="E55">
+      <c r="G55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="F55">
+      <c r="H55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>41</v>
       </c>
-      <c r="B56">
+      <c r="B56" t="str">
+        <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>HUEMUL ENERGÍA SPA</v>
+      </c>
+      <c r="C56">
+        <f>_xlfn.XLOOKUP(A56,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>19</v>
+      </c>
+      <c r="D56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="C56" s="4">
+      <c r="E56" s="4">
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>45.758832419612908</v>
       </c>
-      <c r="D56" s="6">
+      <c r="F56" s="6">
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>44.415675626314659</v>
       </c>
-      <c r="E56">
+      <c r="G56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="F56">
+      <c r="H56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
-      <c r="B57">
+      <c r="B57" t="str">
+        <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ANDES SOLAR II SPA</v>
+      </c>
+      <c r="C57">
+        <f>_xlfn.XLOOKUP(A57,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>21</v>
+      </c>
+      <c r="D57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C57" s="4">
+      <c r="E57" s="4">
         <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>45.353967057396005</v>
       </c>
-      <c r="D57" s="6">
+      <c r="F57" s="6">
         <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>50.634977400775256</v>
       </c>
-      <c r="E57">
+      <c r="G57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F57">
+      <c r="H57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>49</v>
       </c>
-      <c r="B58">
+      <c r="B58" t="str">
+        <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C58">
+        <f>_xlfn.XLOOKUP(A58,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>22</v>
+      </c>
+      <c r="D58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="C58" s="4">
+      <c r="E58" s="4">
         <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>44.183957855804358</v>
       </c>
-      <c r="D58" s="6">
+      <c r="F58" s="6">
         <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>44.183957855804358</v>
       </c>
-      <c r="E58">
+      <c r="G58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F58">
+      <c r="H58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>46</v>
       </c>
-      <c r="B59">
+      <c r="B59" t="str">
+        <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENGIE ENERGÍA CHILE S.A.</v>
+      </c>
+      <c r="C59">
+        <f>_xlfn.XLOOKUP(A59,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>23</v>
+      </c>
+      <c r="D59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="C59" s="4">
+      <c r="E59" s="4">
         <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>39.133131346412249</v>
       </c>
-      <c r="D59" s="6">
+      <c r="F59" s="6">
         <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>38.573698507744766</v>
       </c>
-      <c r="E59">
+      <c r="G59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F59">
+      <c r="H59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
-      <c r="B60">
+      <c r="B60" t="str">
+        <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ENEL GREEN POWER CHILE S.A.</v>
+      </c>
+      <c r="C60">
+        <f>_xlfn.XLOOKUP(A60,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>26</v>
+      </c>
+      <c r="D60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="C60" s="4">
+      <c r="E60" s="4">
         <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>37.517513914770269</v>
       </c>
-      <c r="D60" s="6">
+      <c r="F60" s="6">
         <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>37.517513914770269</v>
       </c>
-      <c r="E60">
+      <c r="G60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F60">
+      <c r="H60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
-      <c r="B61">
+      <c r="B61" t="str">
+        <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>ANDES SOLAR IV SPA</v>
+      </c>
+      <c r="C61">
+        <f>_xlfn.XLOOKUP(A61,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>20</v>
+      </c>
+      <c r="D61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="C61" s="4">
+      <c r="E61" s="4">
         <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>26.715633727325926</v>
       </c>
-      <c r="D61" s="6">
+      <c r="F61" s="6">
         <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>26.715633727325926</v>
       </c>
-      <c r="E61">
+      <c r="G61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F61">
+      <c r="H61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="B62">
+      <c r="B62" t="str">
+        <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
+        <v>GR LIUN SPA</v>
+      </c>
+      <c r="C62">
+        <f>_xlfn.XLOOKUP(A62,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
+        <v>27</v>
+      </c>
+      <c r="D62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="C62" s="4">
+      <c r="E62" s="4">
         <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>20.753233477563935</v>
       </c>
-      <c r="D62" s="6">
+      <c r="F62" s="6">
         <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>20.753233477563935</v>
       </c>
-      <c r="E62">
+      <c r="G62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="F62">
+      <c r="H62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_11358078367124219904/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{56F275FB-DE7A-43AA-BAAA-674B50A9D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EDC80A84-A78D-4B7F-A4DB-B882D25AF553}"/>
+  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{56F275FB-DE7A-43AA-BAAA-674B50A9D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A35A96BD-E9C8-4CA5-868B-A2182E30CE54}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -246,10 +246,13 @@
     <t>Score Comercial Promedio</t>
   </si>
   <si>
-    <t>Score Técnico Promedio 2025</t>
+    <t>Propietario</t>
   </si>
   <si>
-    <t>Propietario</t>
+    <t>Score Técnico 2025</t>
+  </si>
+  <si>
+    <t>¿Tiene BESS?</t>
   </si>
 </sst>
 </file>
@@ -467,6 +470,9 @@
           <cell r="D3" t="str">
             <v>PFV VICTOR JARA</v>
           </cell>
+          <cell r="M3" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD3" t="str">
             <v>-</v>
           </cell>
@@ -481,6 +487,9 @@
           <cell r="D4" t="str">
             <v>PFV ANDES SOLAR III</v>
           </cell>
+          <cell r="M4" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD4" t="str">
             <v>-</v>
           </cell>
@@ -495,6 +504,9 @@
           <cell r="D5" t="str">
             <v>PFV CALEU</v>
           </cell>
+          <cell r="M5" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD5" t="str">
             <v>-</v>
           </cell>
@@ -509,6 +521,9 @@
           <cell r="D6" t="str">
             <v>PFV GRAN TENO</v>
           </cell>
+          <cell r="M6" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD6">
             <v>340.36306314953293</v>
           </cell>
@@ -523,6 +538,9 @@
           <cell r="D7" t="str">
             <v>PFV ANDES SOLAR II</v>
           </cell>
+          <cell r="M7" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD7">
             <v>261.63933396239332</v>
           </cell>
@@ -537,6 +555,9 @@
           <cell r="D8" t="str">
             <v>PFV TAMAYA SOLAR</v>
           </cell>
+          <cell r="M8" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD8">
             <v>258.53120988875185</v>
           </cell>
@@ -551,6 +572,9 @@
           <cell r="D9" t="str">
             <v>PFV DOÑA ANTONIA</v>
           </cell>
+          <cell r="M9" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD9">
             <v>225.14796721950631</v>
           </cell>
@@ -565,6 +589,9 @@
           <cell r="D10" t="str">
             <v>PFV DIEGO DE ALMAGRO</v>
           </cell>
+          <cell r="M10" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD10">
             <v>212.91676434569115</v>
           </cell>
@@ -579,6 +606,9 @@
           <cell r="D11" t="str">
             <v>PFV DOÑA CARMEN SOLAR</v>
           </cell>
+          <cell r="M11" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD11">
             <v>184.07262385643253</v>
           </cell>
@@ -593,6 +623,9 @@
           <cell r="D12" t="str">
             <v>PFV LA HUAYCA II</v>
           </cell>
+          <cell r="M12" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD12">
             <v>182.41667069729561</v>
           </cell>
@@ -607,6 +640,9 @@
           <cell r="D13" t="str">
             <v>PFV CHAÑARES</v>
           </cell>
+          <cell r="M13" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD13">
             <v>178.3717745686545</v>
           </cell>
@@ -621,6 +657,9 @@
           <cell r="D14" t="str">
             <v>PFV MARIA ELENA</v>
           </cell>
+          <cell r="M14" t="str">
+            <v>Existente + Construcción</v>
+          </cell>
           <cell r="CD14">
             <v>165.40925469740816</v>
           </cell>
@@ -635,6 +674,9 @@
           <cell r="D15" t="str">
             <v>PFV QUILAPILUN</v>
           </cell>
+          <cell r="M15" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD15">
             <v>159.96688852477408</v>
           </cell>
@@ -649,6 +691,9 @@
           <cell r="D16" t="str">
             <v>PFV POZO ALMONTE SOLAR III</v>
           </cell>
+          <cell r="M16" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD16">
             <v>155.71867874430706</v>
           </cell>
@@ -663,6 +708,9 @@
           <cell r="D17" t="str">
             <v>PFV CARRERA PINTO</v>
           </cell>
+          <cell r="M17" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD17">
             <v>155.50186037465843</v>
           </cell>
@@ -677,6 +725,9 @@
           <cell r="D18" t="str">
             <v>PFV JAVIERA</v>
           </cell>
+          <cell r="M18" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD18">
             <v>151.54931562087606</v>
           </cell>
@@ -691,6 +742,9 @@
           <cell r="D19" t="str">
             <v>PFV EL ROMERO</v>
           </cell>
+          <cell r="M19" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD19">
             <v>150.53150087405055</v>
           </cell>
@@ -705,6 +759,9 @@
           <cell r="D20" t="str">
             <v>PFV LLANO DE LLAMPOS</v>
           </cell>
+          <cell r="M20" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD20">
             <v>147.10751532332384</v>
           </cell>
@@ -719,6 +776,9 @@
           <cell r="D21" t="str">
             <v>PFV LALACKAMA</v>
           </cell>
+          <cell r="M21" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD21">
             <v>143.37493574349742</v>
           </cell>
@@ -733,6 +793,9 @@
           <cell r="D22" t="str">
             <v>PFV LALACKAMA II</v>
           </cell>
+          <cell r="M22" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD22">
             <v>142.23624220911466</v>
           </cell>
@@ -747,6 +810,9 @@
           <cell r="D23" t="str">
             <v>PFV JAMA</v>
           </cell>
+          <cell r="M23" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD23">
             <v>137.30925624718762</v>
           </cell>
@@ -761,6 +827,9 @@
           <cell r="D24" t="str">
             <v>PFV LUZ DEL NORTE</v>
           </cell>
+          <cell r="M24" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD24">
             <v>134.08829640288874</v>
           </cell>
@@ -775,6 +844,9 @@
           <cell r="D25" t="str">
             <v>PFV DON HUMBERTO</v>
           </cell>
+          <cell r="M25" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD25">
             <v>130.48572110243344</v>
           </cell>
@@ -789,6 +861,9 @@
           <cell r="D26" t="str">
             <v>PFV PAMPA SOLAR NORTE</v>
           </cell>
+          <cell r="M26" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD26">
             <v>127.45927135686706</v>
           </cell>
@@ -803,6 +878,9 @@
           <cell r="D27" t="str">
             <v>PFV CAPRICORNIO</v>
           </cell>
+          <cell r="M27" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD27">
             <v>120.86019668952748</v>
           </cell>
@@ -817,6 +895,9 @@
           <cell r="D28" t="str">
             <v>PFV ANDES SOLAR</v>
           </cell>
+          <cell r="M28" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD28">
             <v>117.00468059513956</v>
           </cell>
@@ -831,6 +912,9 @@
           <cell r="D29" t="str">
             <v>PFV GRANJA SOLAR</v>
           </cell>
+          <cell r="M29" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD29">
             <v>115.95328370578751</v>
           </cell>
@@ -845,6 +929,9 @@
           <cell r="D30" t="str">
             <v>PFV ELENA</v>
           </cell>
+          <cell r="M30" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD30">
             <v>113.47776926480164</v>
           </cell>
@@ -859,6 +946,9 @@
           <cell r="D31" t="str">
             <v>PFV SANTIAGO SOLAR</v>
           </cell>
+          <cell r="M31" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD31">
             <v>106.19134821796176</v>
           </cell>
@@ -873,6 +963,9 @@
           <cell r="D32" t="str">
             <v>PFV FINIS TERRAE</v>
           </cell>
+          <cell r="M32" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD32">
             <v>105.61995670504089</v>
           </cell>
@@ -887,6 +980,9 @@
           <cell r="D33" t="str">
             <v>PFV USYA</v>
           </cell>
+          <cell r="M33" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD33">
             <v>101.99069847540675</v>
           </cell>
@@ -901,6 +997,9 @@
           <cell r="D34" t="str">
             <v>PFV TUTUVEN</v>
           </cell>
+          <cell r="M34" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD34">
             <v>101.75430493021173</v>
           </cell>
@@ -915,6 +1014,9 @@
           <cell r="D35" t="str">
             <v>PFV CONEJO SOLAR</v>
           </cell>
+          <cell r="M35" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD35">
             <v>97.844422713934776</v>
           </cell>
@@ -929,6 +1031,9 @@
           <cell r="D36" t="str">
             <v>PFV SOL DE LOS ANDES</v>
           </cell>
+          <cell r="M36" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD36">
             <v>96.151671241546708</v>
           </cell>
@@ -943,6 +1048,9 @@
           <cell r="D37" t="str">
             <v>PFV DESIERTO DE ATACAMA</v>
           </cell>
+          <cell r="M37" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD37">
             <v>95.889787690443541</v>
           </cell>
@@ -957,6 +1065,9 @@
           <cell r="D38" t="str">
             <v>PFV BOLERO</v>
           </cell>
+          <cell r="M38" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD38">
             <v>95.498581478081192</v>
           </cell>
@@ -971,6 +1082,9 @@
           <cell r="D39" t="str">
             <v>PFV SALVADOR</v>
           </cell>
+          <cell r="M39" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD39">
             <v>93.607486248881401</v>
           </cell>
@@ -985,6 +1099,9 @@
           <cell r="D40" t="str">
             <v>PFV SANTA ISABEL</v>
           </cell>
+          <cell r="M40" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD40">
             <v>92.990504377886353</v>
           </cell>
@@ -999,6 +1116,9 @@
           <cell r="D41" t="str">
             <v>PFV GUANCHOI</v>
           </cell>
+          <cell r="M41" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD41">
             <v>92.236964944062848</v>
           </cell>
@@ -1013,6 +1133,9 @@
           <cell r="D42" t="str">
             <v>PFV SOL DE LILA</v>
           </cell>
+          <cell r="M42" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD42">
             <v>91.398662501573469</v>
           </cell>
@@ -1027,6 +1150,9 @@
           <cell r="D43" t="str">
             <v>PFV AZABACHE</v>
           </cell>
+          <cell r="M43" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD43">
             <v>90.663901448570243</v>
           </cell>
@@ -1041,6 +1167,9 @@
           <cell r="D44" t="str">
             <v>PFV EL PELICANO</v>
           </cell>
+          <cell r="M44" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD44">
             <v>87.353465167615525</v>
           </cell>
@@ -1055,6 +1184,9 @@
           <cell r="D45" t="str">
             <v>PFV CERRO DOMINADOR</v>
           </cell>
+          <cell r="M45" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD45">
             <v>81.329008645014241</v>
           </cell>
@@ -1069,6 +1201,9 @@
           <cell r="D46" t="str">
             <v>PFV URIBE SOLAR</v>
           </cell>
+          <cell r="M46" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD46">
             <v>77.489457860750406</v>
           </cell>
@@ -1083,6 +1218,9 @@
           <cell r="D47" t="str">
             <v>PFV SAN ANDRES</v>
           </cell>
+          <cell r="M47" t="str">
+            <v>Existente + Construcción</v>
+          </cell>
           <cell r="CD47">
             <v>76.428287381574279</v>
           </cell>
@@ -1097,6 +1235,9 @@
           <cell r="D48" t="str">
             <v>PFV NUEVO QUILLAGUA</v>
           </cell>
+          <cell r="M48" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD48">
             <v>74.352491824072459</v>
           </cell>
@@ -1111,6 +1252,9 @@
           <cell r="D49" t="str">
             <v>PFV ALMEYDA</v>
           </cell>
+          <cell r="M49" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD49">
             <v>72.185778981537624</v>
           </cell>
@@ -1125,6 +1269,9 @@
           <cell r="D50" t="str">
             <v>PFV DOMEYKO</v>
           </cell>
+          <cell r="M50" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD50">
             <v>67.586701086894706</v>
           </cell>
@@ -1139,6 +1286,9 @@
           <cell r="D51" t="str">
             <v>PFV NUEVO QUILLAGUA II</v>
           </cell>
+          <cell r="M51" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD51">
             <v>63.442273740022721</v>
           </cell>
@@ -1153,6 +1303,9 @@
           <cell r="D52" t="str">
             <v>PFV RIO ESCONDIDO</v>
           </cell>
+          <cell r="M52" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD52">
             <v>63.352321353673524</v>
           </cell>
@@ -1167,6 +1320,9 @@
           <cell r="D53" t="str">
             <v>PFV LEYDA</v>
           </cell>
+          <cell r="M53" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD53">
             <v>62.577762755201285</v>
           </cell>
@@ -1181,6 +1337,9 @@
           <cell r="D54" t="str">
             <v>PFV ATACAMA SOLAR II</v>
           </cell>
+          <cell r="M54" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD54">
             <v>62.216151585762177</v>
           </cell>
@@ -1195,6 +1354,9 @@
           <cell r="D55" t="str">
             <v>PFV WILLKA</v>
           </cell>
+          <cell r="M55" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD55">
             <v>60.129708168778912</v>
           </cell>
@@ -1209,6 +1371,9 @@
           <cell r="D56" t="str">
             <v>PFV LOS LOROS</v>
           </cell>
+          <cell r="M56" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD56">
             <v>58.793466696212718</v>
           </cell>
@@ -1223,6 +1388,9 @@
           <cell r="D57" t="str">
             <v>PFV SAN PEDRO</v>
           </cell>
+          <cell r="M57" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD57">
             <v>56.184687451190754</v>
           </cell>
@@ -1237,6 +1405,9 @@
           <cell r="D58" t="str">
             <v>PFV LA HUELLA</v>
           </cell>
+          <cell r="M58" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD58">
             <v>56.144466313767701</v>
           </cell>
@@ -1251,6 +1422,9 @@
           <cell r="D59" t="str">
             <v>PFV CEME 1</v>
           </cell>
+          <cell r="M59" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD59">
             <v>54.991027424735762</v>
           </cell>
@@ -1265,6 +1439,9 @@
           <cell r="D60" t="str">
             <v>PFV VALLE ESCONDIDO</v>
           </cell>
+          <cell r="M60" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD60">
             <v>53.365144868727548</v>
           </cell>
@@ -1279,6 +1456,9 @@
           <cell r="D61" t="str">
             <v>PFV MALGARIDA</v>
           </cell>
+          <cell r="M61" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD61">
             <v>52.474910346048155</v>
           </cell>
@@ -1293,6 +1473,9 @@
           <cell r="D62" t="str">
             <v>PFV SOL DEL DESIERTO</v>
           </cell>
+          <cell r="M62" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD62">
             <v>51.957857043217196</v>
           </cell>
@@ -1307,6 +1490,9 @@
           <cell r="D63" t="str">
             <v>PFV TAMARICO</v>
           </cell>
+          <cell r="M63" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD63">
             <v>51.529372024830337</v>
           </cell>
@@ -1321,6 +1507,9 @@
           <cell r="D64" t="str">
             <v>PFV HUATACONDO</v>
           </cell>
+          <cell r="M64" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD64">
             <v>50.304776192582921</v>
           </cell>
@@ -1335,6 +1524,9 @@
           <cell r="D65" t="str">
             <v>PFV TAIRA</v>
           </cell>
+          <cell r="M65" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD65">
             <v>47.729667818285435</v>
           </cell>
@@ -1349,6 +1541,9 @@
           <cell r="D66" t="str">
             <v>PFV LA CRUZ SOLAR</v>
           </cell>
+          <cell r="M66" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD66">
             <v>47.267385112566615</v>
           </cell>
@@ -1363,6 +1558,9 @@
           <cell r="D67" t="str">
             <v>PFV MESETA DE LOS ANDES</v>
           </cell>
+          <cell r="M67" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD67">
             <v>46.921269641603153</v>
           </cell>
@@ -1377,6 +1575,9 @@
           <cell r="D68" t="str">
             <v>PFV VALLE DEL SOL</v>
           </cell>
+          <cell r="M68" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD68">
             <v>46.780683612984056</v>
           </cell>
@@ -1391,6 +1592,9 @@
           <cell r="D69" t="str">
             <v>PFV DIEGO DE ALMAGRO SUR</v>
           </cell>
+          <cell r="M69" t="str">
+            <v>Existente + Construcción</v>
+          </cell>
           <cell r="CD69">
             <v>46.749751407992996</v>
           </cell>
@@ -1405,6 +1609,9 @@
           <cell r="D70" t="str">
             <v>PFV PAMPA TIGRE</v>
           </cell>
+          <cell r="M70" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD70">
             <v>45.758832419612908</v>
           </cell>
@@ -1419,6 +1626,9 @@
           <cell r="D71" t="str">
             <v>PFV ANDES SOLAR II-B</v>
           </cell>
+          <cell r="M71" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD71">
             <v>45.353967057396005</v>
           </cell>
@@ -1433,6 +1643,9 @@
           <cell r="D72" t="str">
             <v>PFV LAS SALINAS</v>
           </cell>
+          <cell r="M72" t="str">
+            <v>Construcción</v>
+          </cell>
           <cell r="CD72">
             <v>44.183957855804358</v>
           </cell>
@@ -1447,6 +1660,9 @@
           <cell r="D73" t="str">
             <v>PFV CAMPOS DEL SOL</v>
           </cell>
+          <cell r="M73" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD73">
             <v>42.05189983405954</v>
           </cell>
@@ -1461,6 +1677,9 @@
           <cell r="D74" t="str">
             <v>PFV CHERCAN SOLAR</v>
           </cell>
+          <cell r="M74" t="str">
+            <v>-</v>
+          </cell>
           <cell r="CD74">
             <v>41.377677526356848</v>
           </cell>
@@ -1475,6 +1694,9 @@
           <cell r="D75" t="str">
             <v>PFV COYA</v>
           </cell>
+          <cell r="M75" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD75">
             <v>39.133131346412249</v>
           </cell>
@@ -1489,6 +1711,9 @@
           <cell r="D76" t="str">
             <v>PFV MANZANO</v>
           </cell>
+          <cell r="M76" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD76">
             <v>37.517513914770269</v>
           </cell>
@@ -1503,6 +1728,9 @@
           <cell r="D77" t="str">
             <v>PFV ANDES SOLAR IV</v>
           </cell>
+          <cell r="M77" t="str">
+            <v>Existente</v>
+          </cell>
           <cell r="CD77">
             <v>26.715633727325926</v>
           </cell>
@@ -1516,6 +1744,9 @@
           </cell>
           <cell r="D78" t="str">
             <v>PFV TAMANGO</v>
+          </cell>
+          <cell r="M78" t="str">
+            <v>Construcción</v>
           </cell>
           <cell r="CD78">
             <v>20.753233477563935</v>
@@ -16229,45 +16460,49 @@
   <sheetPr>
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
-  <dimension ref="A1:H62"/>
+  <dimension ref="A1:I62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="47.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.5703125" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" customWidth="1"/>
-    <col min="5" max="6" width="16.28515625" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" customWidth="1"/>
+    <col min="6" max="7" width="16.28515625" customWidth="1"/>
+    <col min="8" max="8" width="13" customWidth="1"/>
+    <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -16275,32 +16510,36 @@
         <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>GR CHAÑAR SPA</v>
       </c>
-      <c r="C2">
+      <c r="C2" t="str">
+        <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D2">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="E2" s="4" t="str">
+      <c r="F2" s="4" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="F2" s="6" t="str">
+      <c r="G2" s="6" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="H2" t="str">
+      <c r="I2" t="str">
         <f>_xlfn.XLOOKUP(A2,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -16308,32 +16547,36 @@
         <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ANDES SOLAR III SPA</v>
       </c>
-      <c r="C3">
+      <c r="C3" t="str">
+        <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D3">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="str">
+      <c r="F3" s="4" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="F3" s="6" t="str">
+      <c r="G3" s="6" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="G3" t="str">
+      <c r="H3" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="H3" t="str">
+      <c r="I3" t="str">
         <f>_xlfn.XLOOKUP(A3,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -16341,32 +16584,36 @@
         <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>GR ALGARROBO SPA</v>
       </c>
-      <c r="C4">
+      <c r="C4" t="str">
+        <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="E4" s="4">
+      <c r="F4" s="4">
         <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>340.36306314953293</v>
       </c>
-      <c r="F4" s="6">
+      <c r="G4" s="6">
         <f>_xlfn.XLOOKUP(A4,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>340.36306314953293</v>
       </c>
-      <c r="G4">
+      <c r="H4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H4">
+      <c r="I4">
         <f>_xlfn.XLOOKUP(A4,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -16374,32 +16621,36 @@
         <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ANDES SOLAR II SPA</v>
       </c>
-      <c r="C5">
+      <c r="C5" t="str">
+        <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E5" s="4">
+      <c r="F5" s="4">
         <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>261.63933396239332</v>
       </c>
-      <c r="F5" s="6">
+      <c r="G5" s="6">
         <f>_xlfn.XLOOKUP(A5,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>154.25090610149064</v>
       </c>
-      <c r="G5">
+      <c r="H5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H5">
+      <c r="I5">
         <f>_xlfn.XLOOKUP(A5,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -16407,32 +16658,36 @@
         <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENGIE ENERGÍA CHILE S.A.</v>
       </c>
-      <c r="C6">
+      <c r="C6" t="str">
+        <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E6" s="4">
+      <c r="F6" s="4">
         <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>258.53120988875185</v>
       </c>
-      <c r="F6" s="6">
+      <c r="G6" s="6">
         <f>_xlfn.XLOOKUP(A6,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>116.69232684199737</v>
       </c>
-      <c r="G6">
+      <c r="H6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H6">
+      <c r="I6">
         <f>_xlfn.XLOOKUP(A6,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -16440,32 +16695,36 @@
         <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>DOÑA ANTONIA SOLAR SPA</v>
       </c>
-      <c r="C7">
+      <c r="C7" t="str">
+        <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>37</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>37</v>
       </c>
-      <c r="E7" s="4">
+      <c r="F7" s="4">
         <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>225.14796721950631</v>
       </c>
-      <c r="F7" s="6">
+      <c r="G7" s="6">
         <f>_xlfn.XLOOKUP(A7,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>225.14796721950631</v>
       </c>
-      <c r="G7">
+      <c r="H7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H7">
+      <c r="I7">
         <f>_xlfn.XLOOKUP(A7,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -16473,32 +16732,36 @@
         <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
       </c>
-      <c r="C8">
+      <c r="C8" t="str">
+        <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>31</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="E8" s="4">
+      <c r="F8" s="4">
         <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>212.91676434569115</v>
       </c>
-      <c r="F8" s="6">
+      <c r="G8" s="6">
         <f>_xlfn.XLOOKUP(A8,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>190.90031470068843</v>
       </c>
-      <c r="G8">
+      <c r="H8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H8">
+      <c r="I8">
         <f>_xlfn.XLOOKUP(A8,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -16506,32 +16769,36 @@
         <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENERGÍA CERRO EL MORADO S.A.</v>
       </c>
-      <c r="C9">
+      <c r="C9" t="str">
+        <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E9" s="4">
+      <c r="F9" s="4">
         <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>184.07262385643253</v>
       </c>
-      <c r="F9" s="6">
+      <c r="G9" s="6">
         <f>_xlfn.XLOOKUP(A9,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>173.34955912683731</v>
       </c>
-      <c r="G9">
+      <c r="H9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H9">
+      <c r="I9">
         <f>_xlfn.XLOOKUP(A9,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -16539,32 +16806,36 @@
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENLIGHT INVESTMENTS SPA</v>
       </c>
-      <c r="C10">
+      <c r="C10" t="str">
+        <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>31</v>
       </c>
-      <c r="E10" s="4">
+      <c r="F10" s="4">
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>182.41667069729561</v>
       </c>
-      <c r="F10" s="6">
+      <c r="G10" s="6">
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>145.62272360314196</v>
       </c>
-      <c r="G10">
+      <c r="H10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H10">
+      <c r="I10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -16572,32 +16843,36 @@
         <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C11">
+      <c r="C11" t="str">
+        <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="E11" s="4">
+      <c r="F11" s="4">
         <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>178.3717745686545</v>
       </c>
-      <c r="F11" s="6">
+      <c r="G11" s="6">
         <f>_xlfn.XLOOKUP(A11,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>160.32307404988748</v>
       </c>
-      <c r="G11">
+      <c r="H11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>10</v>
       </c>
-      <c r="H11">
+      <c r="I11">
         <f>_xlfn.XLOOKUP(A11,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -16605,32 +16880,36 @@
         <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>GENERACIÓN SOLAR SPA</v>
       </c>
-      <c r="C12">
+      <c r="C12" t="str">
+        <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente + Construcción</v>
+      </c>
+      <c r="D12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>36</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="E12" s="4">
+      <c r="F12" s="4">
         <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>165.40925469740816</v>
       </c>
-      <c r="F12" s="6">
+      <c r="G12" s="6">
         <f>_xlfn.XLOOKUP(A12,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>164.3939197409471</v>
       </c>
-      <c r="G12">
+      <c r="H12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H12">
+      <c r="I12">
         <f>_xlfn.XLOOKUP(A12,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -16638,32 +16917,36 @@
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CHUNGUNGO S.A.</v>
       </c>
-      <c r="C13">
+      <c r="C13" t="str">
+        <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E13" s="4">
+      <c r="F13" s="4">
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>159.96688852477408</v>
       </c>
-      <c r="F13" s="6">
+      <c r="G13" s="6">
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>150.66054694362239</v>
       </c>
-      <c r="G13">
+      <c r="H13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H13">
+      <c r="I13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -16671,32 +16954,36 @@
         <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
       </c>
-      <c r="C14">
+      <c r="C14" t="str">
+        <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E14" s="4">
+      <c r="F14" s="4">
         <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>155.50186037465843</v>
       </c>
-      <c r="F14" s="6">
+      <c r="G14" s="6">
         <f>_xlfn.XLOOKUP(A14,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>131.2541894992178</v>
       </c>
-      <c r="G14">
+      <c r="H14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H14">
+      <c r="I14">
         <f>_xlfn.XLOOKUP(A14,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -16704,32 +16991,36 @@
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>JAVIERA SPA</v>
       </c>
-      <c r="C15">
+      <c r="C15" t="str">
+        <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D15">
+      <c r="E15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E15" s="4">
+      <c r="F15" s="4">
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>151.54931562087606</v>
       </c>
-      <c r="F15" s="6">
+      <c r="G15" s="6">
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>153.36115611189666</v>
       </c>
-      <c r="G15">
+      <c r="H15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H15">
+      <c r="I15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -16737,32 +17028,36 @@
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C16">
+      <c r="C16" t="str">
+        <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D16">
+      <c r="E16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E16" s="4">
+      <c r="F16" s="4">
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>150.53150087405055</v>
       </c>
-      <c r="F16" s="6">
+      <c r="G16" s="6">
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>126.29025312310564</v>
       </c>
-      <c r="G16">
+      <c r="H16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H16">
+      <c r="I16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -16770,32 +17065,36 @@
         <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>AMANECER SOLAR SPA</v>
       </c>
-      <c r="C17">
+      <c r="C17" t="str">
+        <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="D17">
+      <c r="E17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E17" s="4">
+      <c r="F17" s="4">
         <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>147.10751532332384</v>
       </c>
-      <c r="F17" s="6">
+      <c r="G17" s="6">
         <f>_xlfn.XLOOKUP(A17,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>142.61474714826912</v>
       </c>
-      <c r="G17">
+      <c r="H17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>9</v>
       </c>
-      <c r="H17">
+      <c r="I17">
         <f>_xlfn.XLOOKUP(A17,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -16803,32 +17102,36 @@
         <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C18">
+      <c r="C18" t="str">
+        <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D18">
+      <c r="E18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="E18" s="4">
+      <c r="F18" s="4">
         <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>143.37493574349742</v>
       </c>
-      <c r="F18" s="6">
+      <c r="G18" s="6">
         <f>_xlfn.XLOOKUP(A18,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>133.7946701446663</v>
       </c>
-      <c r="G18">
+      <c r="H18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H18">
+      <c r="I18">
         <f>_xlfn.XLOOKUP(A18,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -16836,32 +17139,36 @@
         <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PLANTA SOLAR SAN PEDRO III SPA</v>
       </c>
-      <c r="C19">
+      <c r="C19" t="str">
+        <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="D19">
+      <c r="E19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E19" s="4">
+      <c r="F19" s="4">
         <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>137.30925624718762</v>
       </c>
-      <c r="F19" s="6">
+      <c r="G19" s="6">
         <f>_xlfn.XLOOKUP(A19,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>123.4689482698556</v>
       </c>
-      <c r="G19">
+      <c r="H19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H19">
+      <c r="I19">
         <f>_xlfn.XLOOKUP(A19,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -16869,32 +17176,36 @@
         <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PARQUE SOLAR FOTOVOLTAICO LUZ DEL NORTE SPA</v>
       </c>
-      <c r="C20">
+      <c r="C20" t="str">
+        <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>31</v>
       </c>
-      <c r="D20">
+      <c r="E20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="E20" s="4">
+      <c r="F20" s="4">
         <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>134.08829640288874</v>
       </c>
-      <c r="F20" s="6">
+      <c r="G20" s="6">
         <f>_xlfn.XLOOKUP(A20,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>118.82812570112476</v>
       </c>
-      <c r="G20">
+      <c r="H20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H20">
+      <c r="I20">
         <f>_xlfn.XLOOKUP(A20,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -16902,32 +17213,36 @@
         <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C21">
+      <c r="C21" t="str">
+        <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D21">
+      <c r="E21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="E21" s="4">
+      <c r="F21" s="4">
         <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>130.48572110243344</v>
       </c>
-      <c r="F21" s="6">
+      <c r="G21" s="6">
         <f>_xlfn.XLOOKUP(A21,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>130.48572110243344</v>
       </c>
-      <c r="G21">
+      <c r="H21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H21">
+      <c r="I21">
         <f>_xlfn.XLOOKUP(A21,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -16935,32 +17250,36 @@
         <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ARCADIA GENERACIÓN SOLAR S.A.</v>
       </c>
-      <c r="C22">
+      <c r="C22" t="str">
+        <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D22">
+      <c r="E22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E22" s="4">
+      <c r="F22" s="4">
         <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>127.45927135686706</v>
       </c>
-      <c r="F22" s="6">
+      <c r="G22" s="6">
         <f>_xlfn.XLOOKUP(A22,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>117.55952975574159</v>
       </c>
-      <c r="G22">
+      <c r="H22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H22">
+      <c r="I22">
         <f>_xlfn.XLOOKUP(A22,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -16968,32 +17287,36 @@
         <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENGIE ENERGÍA CHILE S.A.</v>
       </c>
-      <c r="C23">
+      <c r="C23" t="str">
+        <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="D23">
+      <c r="E23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="E23" s="4">
+      <c r="F23" s="4">
         <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>120.86019668952748</v>
       </c>
-      <c r="F23" s="6">
+      <c r="G23" s="6">
         <f>_xlfn.XLOOKUP(A23,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>77.673577614814533</v>
       </c>
-      <c r="G23">
+      <c r="H23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>8</v>
       </c>
-      <c r="H23">
+      <c r="I23">
         <f>_xlfn.XLOOKUP(A23,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -17001,32 +17324,36 @@
         <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ANDES SOLAR SPA</v>
       </c>
-      <c r="C24">
+      <c r="C24" t="str">
+        <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="E24" s="4">
+      <c r="F24" s="4">
         <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>117.00468059513956</v>
       </c>
-      <c r="F24" s="6">
+      <c r="G24" s="6">
         <f>_xlfn.XLOOKUP(A24,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>107.06022465930636</v>
       </c>
-      <c r="G24">
+      <c r="H24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="H24">
+      <c r="I24">
         <f>_xlfn.XLOOKUP(A24,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -17034,32 +17361,36 @@
         <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>COPEC RENOVABLES SPA</v>
       </c>
-      <c r="C25">
+      <c r="C25" t="str">
+        <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E25" s="4">
+      <c r="F25" s="4">
         <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>115.95328370578751</v>
       </c>
-      <c r="F25" s="6">
+      <c r="G25" s="6">
         <f>_xlfn.XLOOKUP(A25,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>73.249911595920381</v>
       </c>
-      <c r="G25">
+      <c r="H25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="H25">
+      <c r="I25">
         <f>_xlfn.XLOOKUP(A25,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -17067,32 +17398,36 @@
         <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>SOLAR ELENA SPA</v>
       </c>
-      <c r="C26">
+      <c r="C26" t="str">
+        <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E26" s="4">
+      <c r="F26" s="4">
         <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>113.47776926480164</v>
       </c>
-      <c r="F26" s="6">
+      <c r="G26" s="6">
         <f>_xlfn.XLOOKUP(A26,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>77.517731576601136</v>
       </c>
-      <c r="G26">
+      <c r="H26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="H26">
+      <c r="I26">
         <f>_xlfn.XLOOKUP(A26,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -17100,32 +17435,36 @@
         <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>SANTIAGO SOLAR S.A.</v>
       </c>
-      <c r="C27">
+      <c r="C27" t="str">
+        <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D27">
+      <c r="E27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E27" s="4">
+      <c r="F27" s="4">
         <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>106.19134821796176</v>
       </c>
-      <c r="F27" s="6">
+      <c r="G27" s="6">
         <f>_xlfn.XLOOKUP(A27,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>106.46671004953231</v>
       </c>
-      <c r="G27">
+      <c r="H27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="H27">
+      <c r="I27">
         <f>_xlfn.XLOOKUP(A27,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -17133,32 +17472,36 @@
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C28">
+      <c r="C28" t="str">
+        <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D28">
+      <c r="E28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E28" s="4">
+      <c r="F28" s="4">
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>101.99069847540675</v>
       </c>
-      <c r="F28" s="6">
+      <c r="G28" s="6">
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>71.964555409210689</v>
       </c>
-      <c r="G28">
+      <c r="H28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>7</v>
       </c>
-      <c r="H28">
+      <c r="I28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -17166,32 +17509,36 @@
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CONEJO SOLAR SPA</v>
       </c>
-      <c r="C29">
+      <c r="C29" t="str">
+        <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="D29">
+      <c r="E29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="E29" s="4">
+      <c r="F29" s="4">
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>97.844422713934776</v>
       </c>
-      <c r="F29" s="6">
+      <c r="G29" s="6">
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>97.238183111387499</v>
       </c>
-      <c r="G29">
+      <c r="H29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="H29">
+      <c r="I29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -17199,32 +17546,36 @@
         <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>OPDENERGY GENERACIÓN SPA</v>
       </c>
-      <c r="C30">
+      <c r="C30" t="str">
+        <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D30">
+      <c r="E30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="E30" s="4">
+      <c r="F30" s="4">
         <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>96.151671241546708</v>
       </c>
-      <c r="F30" s="6">
+      <c r="G30" s="6">
         <f>_xlfn.XLOOKUP(A30,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>63.301005566807682</v>
       </c>
-      <c r="G30">
+      <c r="H30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="H30">
+      <c r="I30">
         <f>_xlfn.XLOOKUP(A30,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -17232,32 +17583,36 @@
         <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>BOLERO SPA</v>
       </c>
-      <c r="C31">
+      <c r="C31" t="str">
+        <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>29</v>
       </c>
-      <c r="D31">
+      <c r="E31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E31" s="4">
+      <c r="F31" s="4">
         <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>95.498581478081192</v>
       </c>
-      <c r="F31" s="6">
+      <c r="G31" s="6">
         <f>_xlfn.XLOOKUP(A31,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>91.571363913723303</v>
       </c>
-      <c r="G31">
+      <c r="H31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="H31">
+      <c r="I31">
         <f>_xlfn.XLOOKUP(A31,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -17265,32 +17620,36 @@
         <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>AELA GENERACIÓN S.A.</v>
       </c>
-      <c r="C32">
+      <c r="C32" t="str">
+        <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D32">
+      <c r="E32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="E32" s="4">
+      <c r="F32" s="4">
         <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>93.607486248881401</v>
       </c>
-      <c r="F32" s="6">
+      <c r="G32" s="6">
         <f>_xlfn.XLOOKUP(A32,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>279.63938708891095</v>
       </c>
-      <c r="G32">
+      <c r="H32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="H32">
+      <c r="I32">
         <f>_xlfn.XLOOKUP(A32,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -17298,32 +17657,36 @@
         <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>TSGF SPA</v>
       </c>
-      <c r="C33">
+      <c r="C33" t="str">
+        <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>33</v>
       </c>
-      <c r="D33">
+      <c r="E33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>30</v>
       </c>
-      <c r="E33" s="4">
+      <c r="F33" s="4">
         <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>92.990504377886353</v>
       </c>
-      <c r="F33" s="6">
+      <c r="G33" s="6">
         <f>_xlfn.XLOOKUP(A33,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>137.26143535275247</v>
       </c>
-      <c r="G33">
+      <c r="H33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>6</v>
       </c>
-      <c r="H33">
+      <c r="I33">
         <f>_xlfn.XLOOKUP(A33,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -17331,32 +17694,36 @@
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C34">
+      <c r="C34" t="str">
+        <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="D34">
+      <c r="E34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E34" s="4">
+      <c r="F34" s="4">
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>91.398662501573469</v>
       </c>
-      <c r="F34" s="6">
+      <c r="G34" s="6">
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.595599722111082</v>
       </c>
-      <c r="G34">
+      <c r="H34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H34">
+      <c r="I34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -17364,32 +17731,36 @@
         <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C35">
+      <c r="C35" t="str">
+        <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E35" s="4">
+      <c r="F35" s="4">
         <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>90.663901448570243</v>
       </c>
-      <c r="F35" s="6">
+      <c r="G35" s="6">
         <f>_xlfn.XLOOKUP(A35,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.308560240126781</v>
       </c>
-      <c r="G35">
+      <c r="H35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H35">
+      <c r="I35">
         <f>_xlfn.XLOOKUP(A35,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -17397,32 +17768,36 @@
         <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>EL PELÍCANO SOLAR COMPANY SPA</v>
       </c>
-      <c r="C36">
+      <c r="C36" t="str">
+        <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E36" s="4">
+      <c r="F36" s="4">
         <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>87.353465167615525</v>
       </c>
-      <c r="F36" s="6">
+      <c r="G36" s="6">
         <f>_xlfn.XLOOKUP(A36,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>85.46269087234684</v>
       </c>
-      <c r="G36">
+      <c r="H36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H36">
+      <c r="I36">
         <f>_xlfn.XLOOKUP(A36,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -17430,32 +17805,36 @@
         <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CERRO DOMINADOR CSP S.A.</v>
       </c>
-      <c r="C37">
+      <c r="C37" t="str">
+        <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>17</v>
       </c>
-      <c r="E37" s="4">
+      <c r="F37" s="4">
         <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>81.329008645014241</v>
       </c>
-      <c r="F37" s="6">
+      <c r="G37" s="6">
         <f>_xlfn.XLOOKUP(A37,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>78.097831211286106</v>
       </c>
-      <c r="G37">
+      <c r="H37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H37">
+      <c r="I37">
         <f>_xlfn.XLOOKUP(A37,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -17463,32 +17842,36 @@
         <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
       </c>
-      <c r="C38">
+      <c r="C38" t="str">
+        <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D38">
+      <c r="E38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E38" s="4">
+      <c r="F38" s="4">
         <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>77.489457860750406</v>
       </c>
-      <c r="F38" s="6">
+      <c r="G38" s="6">
         <f>_xlfn.XLOOKUP(A38,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>96.082038641272788</v>
       </c>
-      <c r="G38">
+      <c r="H38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H38">
+      <c r="I38">
         <f>_xlfn.XLOOKUP(A38,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -17496,32 +17879,36 @@
         <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>AELA GENERACIÓN S.A.</v>
       </c>
-      <c r="C39">
+      <c r="C39" t="str">
+        <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente + Construcción</v>
+      </c>
+      <c r="D39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D39">
+      <c r="E39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E39" s="4">
+      <c r="F39" s="4">
         <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>76.428287381574279</v>
       </c>
-      <c r="F39" s="6">
+      <c r="G39" s="6">
         <f>_xlfn.XLOOKUP(A39,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>213.69474255136006</v>
       </c>
-      <c r="G39">
+      <c r="H39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H39">
+      <c r="I39">
         <f>_xlfn.XLOOKUP(A39,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -17529,32 +17916,36 @@
         <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
       </c>
-      <c r="C40">
+      <c r="C40" t="str">
+        <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="D40">
+      <c r="E40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>18</v>
       </c>
-      <c r="E40" s="4">
+      <c r="F40" s="4">
         <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>74.352491824072459</v>
       </c>
-      <c r="F40" s="6">
+      <c r="G40" s="6">
         <f>_xlfn.XLOOKUP(A40,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>62.959486745461732</v>
       </c>
-      <c r="G40">
+      <c r="H40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H40">
+      <c r="I40">
         <f>_xlfn.XLOOKUP(A40,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -17562,32 +17953,36 @@
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C41">
+      <c r="C41" t="str">
+        <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>31</v>
       </c>
-      <c r="D41">
+      <c r="E41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E41" s="4">
+      <c r="F41" s="4">
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>72.185778981537624</v>
       </c>
-      <c r="F41" s="6">
+      <c r="G41" s="6">
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>56.377157688509307</v>
       </c>
-      <c r="G41">
+      <c r="H41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>5</v>
       </c>
-      <c r="H41">
+      <c r="I41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -17595,32 +17990,36 @@
         <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PARQUE FOTOVOLTAICO NUEVO QUILLAGUA SPA</v>
       </c>
-      <c r="C42">
+      <c r="C42" t="str">
+        <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D42">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="D42">
+      <c r="E42">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E42" s="4">
+      <c r="F42" s="4">
         <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>63.442273740022721</v>
       </c>
-      <c r="F42" s="6" t="str">
+      <c r="G42" s="6" t="str">
         <f>_xlfn.XLOOKUP(A42,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="G42">
+      <c r="H42">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H42" t="str">
+      <c r="I42" t="str">
         <f>_xlfn.XLOOKUP(A42,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -17628,32 +18027,36 @@
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CÓNDOR ENERGÍA SPA</v>
       </c>
-      <c r="C43">
+      <c r="C43" t="str">
+        <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D43">
+      <c r="E43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E43" s="4">
+      <c r="F43" s="4">
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>63.352321353673524</v>
       </c>
-      <c r="F43" s="6">
+      <c r="G43" s="6">
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>58.213209897553845</v>
       </c>
-      <c r="G43">
+      <c r="H43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H43">
+      <c r="I43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -17661,32 +18064,36 @@
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PARQUE SOLAR LEYDA SPA</v>
       </c>
-      <c r="C44">
+      <c r="C44" t="str">
+        <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D44">
+      <c r="E44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E44" s="4">
+      <c r="F44" s="4">
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>62.577762755201285</v>
       </c>
-      <c r="F44" s="6" t="str">
+      <c r="G44" s="6" t="str">
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="G44">
+      <c r="H44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H44" t="str">
+      <c r="I44" t="str">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -17694,32 +18101,36 @@
         <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ATACAMA SOLAR SPA</v>
       </c>
-      <c r="C45">
+      <c r="C45" t="str">
+        <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D45">
+      <c r="E45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E45" s="4">
+      <c r="F45" s="4">
         <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>62.216151585762177</v>
       </c>
-      <c r="F45" s="6">
+      <c r="G45" s="6">
         <f>_xlfn.XLOOKUP(A45,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>51.173475954890485</v>
       </c>
-      <c r="G45">
+      <c r="H45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H45">
+      <c r="I45">
         <f>_xlfn.XLOOKUP(A45,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -17727,32 +18138,36 @@
         <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>INVERSIONES FOTOVOLTAICAS SPA</v>
       </c>
-      <c r="C46">
+      <c r="C46" t="str">
+        <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E46" s="4">
+      <c r="F46" s="4">
         <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>60.129708168778912</v>
       </c>
-      <c r="F46" s="6">
+      <c r="G46" s="6">
         <f>_xlfn.XLOOKUP(A46,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>60.129708168778912</v>
       </c>
-      <c r="G46">
+      <c r="H46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H46">
+      <c r="I46">
         <f>_xlfn.XLOOKUP(A46,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -17760,32 +18175,36 @@
         <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>SOLAR LOS LOROS SPA</v>
       </c>
-      <c r="C47">
+      <c r="C47" t="str">
+        <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="E47" s="4">
+      <c r="F47" s="4">
         <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>58.793466696212718</v>
       </c>
-      <c r="F47" s="6">
+      <c r="G47" s="6">
         <f>_xlfn.XLOOKUP(A47,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>98.698739826924182</v>
       </c>
-      <c r="G47">
+      <c r="H47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>4</v>
       </c>
-      <c r="H47">
+      <c r="I47">
         <f>_xlfn.XLOOKUP(A47,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -17793,32 +18212,36 @@
         <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>IBEREÓLICA CABO LEONES II S.A.</v>
       </c>
-      <c r="C48">
+      <c r="C48" t="str">
+        <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E48" s="4">
+      <c r="F48" s="4">
         <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>56.184687451190754</v>
       </c>
-      <c r="F48" s="6">
+      <c r="G48" s="6">
         <f>_xlfn.XLOOKUP(A48,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>51.658946411605257</v>
       </c>
-      <c r="G48">
+      <c r="H48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="H48">
+      <c r="I48">
         <f>_xlfn.XLOOKUP(A48,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -17826,32 +18249,36 @@
         <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>AUSTRIANSOLAR CHILE SEIS SPA</v>
       </c>
-      <c r="C49">
+      <c r="C49" t="str">
+        <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="E49" s="4">
+      <c r="F49" s="4">
         <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>56.144466313767701</v>
       </c>
-      <c r="F49" s="6">
+      <c r="G49" s="6">
         <f>_xlfn.XLOOKUP(A49,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>53.422824583531359</v>
       </c>
-      <c r="G49">
+      <c r="H49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="H49">
+      <c r="I49">
         <f>_xlfn.XLOOKUP(A49,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -17859,32 +18286,36 @@
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>HUEMUL ENERGÍA SPA</v>
       </c>
-      <c r="C50">
+      <c r="C50" t="str">
+        <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D50">
+      <c r="E50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>24</v>
       </c>
-      <c r="E50" s="4">
+      <c r="F50" s="4">
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>53.365144868727548</v>
       </c>
-      <c r="F50" s="6">
+      <c r="G50" s="6">
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>48.561374555411653</v>
       </c>
-      <c r="G50">
+      <c r="H50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="H50">
+      <c r="I50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -17892,32 +18323,36 @@
         <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>TAMARICO SOLAR DOS SPA</v>
       </c>
-      <c r="C51">
+      <c r="C51" t="str">
+        <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D51">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="D51">
+      <c r="E51">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>28</v>
       </c>
-      <c r="E51" s="4">
+      <c r="F51" s="4">
         <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>51.529372024830337</v>
       </c>
-      <c r="F51" s="6" t="str">
+      <c r="G51" s="6" t="str">
         <f>_xlfn.XLOOKUP(A51,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>-</v>
       </c>
-      <c r="G51">
+      <c r="H51">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>3</v>
       </c>
-      <c r="H51" t="str">
+      <c r="I51" t="str">
         <f>_xlfn.XLOOKUP(A51,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -17925,32 +18360,36 @@
         <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>AUSTRIANSOLAR CHILE CUATRO SPA</v>
       </c>
-      <c r="C52">
+      <c r="C52" t="str">
+        <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="D52">
+      <c r="E52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>25</v>
       </c>
-      <c r="E52" s="4">
+      <c r="F52" s="4">
         <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>50.304776192582921</v>
       </c>
-      <c r="F52" s="6">
+      <c r="G52" s="6">
         <f>_xlfn.XLOOKUP(A52,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>60.987509864450338</v>
       </c>
-      <c r="G52">
+      <c r="H52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="H52">
+      <c r="I52">
         <f>_xlfn.XLOOKUP(A52,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -17958,32 +18397,36 @@
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
       </c>
-      <c r="C53">
+      <c r="C53" t="str">
+        <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="D53">
+      <c r="E53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="E53" s="4">
+      <c r="F53" s="4">
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>47.267385112566615</v>
       </c>
-      <c r="F53" s="6">
+      <c r="G53" s="6">
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>43.797716855137359</v>
       </c>
-      <c r="G53">
+      <c r="H53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="H53">
+      <c r="I53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -17991,32 +18434,36 @@
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>SONNEDIX COX ENERGY CHILE SPA</v>
       </c>
-      <c r="C54">
+      <c r="C54" t="str">
+        <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D54">
+      <c r="E54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E54" s="4">
+      <c r="F54" s="4">
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>46.921269641603153</v>
       </c>
-      <c r="F54" s="6">
+      <c r="G54" s="6">
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>53.406650841276864</v>
       </c>
-      <c r="G54">
+      <c r="H54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="H54">
+      <c r="I54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -18024,32 +18471,36 @@
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C55">
+      <c r="C55" t="str">
+        <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D55">
+      <c r="E55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="E55" s="4">
+      <c r="F55" s="4">
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>46.780683612984056</v>
       </c>
-      <c r="F55" s="6">
+      <c r="G55" s="6">
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>45.575537933172924</v>
       </c>
-      <c r="G55">
+      <c r="H55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="H55">
+      <c r="I55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -18057,32 +18508,36 @@
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>HUEMUL ENERGÍA SPA</v>
       </c>
-      <c r="C56">
+      <c r="C56" t="str">
+        <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>-</v>
+      </c>
+      <c r="D56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>19</v>
       </c>
-      <c r="D56">
+      <c r="E56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="E56" s="4">
+      <c r="F56" s="4">
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>45.758832419612908</v>
       </c>
-      <c r="F56" s="6">
+      <c r="G56" s="6">
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>44.415675626314659</v>
       </c>
-      <c r="G56">
+      <c r="H56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>2</v>
       </c>
-      <c r="H56">
+      <c r="I56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -18090,32 +18545,36 @@
         <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ANDES SOLAR II SPA</v>
       </c>
-      <c r="C57">
+      <c r="C57" t="str">
+        <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>21</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E57" s="4">
+      <c r="F57" s="4">
         <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>45.353967057396005</v>
       </c>
-      <c r="F57" s="6">
+      <c r="G57" s="6">
         <f>_xlfn.XLOOKUP(A57,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>50.634977400775256</v>
       </c>
-      <c r="G57">
+      <c r="H57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H57">
+      <c r="I57">
         <f>_xlfn.XLOOKUP(A57,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -18123,32 +18582,36 @@
         <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C58">
+      <c r="C58" t="str">
+        <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>22</v>
       </c>
-      <c r="E58" s="4">
+      <c r="F58" s="4">
         <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>44.183957855804358</v>
       </c>
-      <c r="F58" s="6">
+      <c r="G58" s="6">
         <f>_xlfn.XLOOKUP(A58,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>44.183957855804358</v>
       </c>
-      <c r="G58">
+      <c r="H58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H58">
+      <c r="I58">
         <f>_xlfn.XLOOKUP(A58,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>46</v>
       </c>
@@ -18156,32 +18619,36 @@
         <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENGIE ENERGÍA CHILE S.A.</v>
       </c>
-      <c r="C59">
+      <c r="C59" t="str">
+        <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>23</v>
       </c>
-      <c r="E59" s="4">
+      <c r="F59" s="4">
         <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>39.133131346412249</v>
       </c>
-      <c r="F59" s="6">
+      <c r="G59" s="6">
         <f>_xlfn.XLOOKUP(A59,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>38.573698507744766</v>
       </c>
-      <c r="G59">
+      <c r="H59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H59">
+      <c r="I59">
         <f>_xlfn.XLOOKUP(A59,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -18189,32 +18656,36 @@
         <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C60">
+      <c r="C60" t="str">
+        <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>26</v>
       </c>
-      <c r="E60" s="4">
+      <c r="F60" s="4">
         <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>37.517513914770269</v>
       </c>
-      <c r="F60" s="6">
+      <c r="G60" s="6">
         <f>_xlfn.XLOOKUP(A60,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>37.517513914770269</v>
       </c>
-      <c r="G60">
+      <c r="H60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H60">
+      <c r="I60">
         <f>_xlfn.XLOOKUP(A60,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -18222,32 +18693,36 @@
         <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ANDES SOLAR IV SPA</v>
       </c>
-      <c r="C61">
+      <c r="C61" t="str">
+        <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Existente</v>
+      </c>
+      <c r="D61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="D61">
+      <c r="E61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>20</v>
       </c>
-      <c r="E61" s="4">
+      <c r="F61" s="4">
         <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>26.715633727325926</v>
       </c>
-      <c r="F61" s="6">
+      <c r="G61" s="6">
         <f>_xlfn.XLOOKUP(A61,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>26.715633727325926</v>
       </c>
-      <c r="G61">
+      <c r="H61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H61">
+      <c r="I61">
         <f>_xlfn.XLOOKUP(A61,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>56</v>
       </c>
@@ -18255,27 +18730,31 @@
         <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>GR LIUN SPA</v>
       </c>
-      <c r="C62">
+      <c r="C62" t="str">
+        <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
+        <v>Construcción</v>
+      </c>
+      <c r="D62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="D62">
+      <c r="E62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE Técnico Promedio'!A$30:A$761,'[1]SCORE Técnico Promedio'!M$30:M$761,"---",0,1)</f>
         <v>27</v>
       </c>
-      <c r="E62" s="4">
+      <c r="F62" s="4">
         <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CD$3:CD$78,"---",0,1)</f>
         <v>20.753233477563935</v>
       </c>
-      <c r="F62" s="6">
+      <c r="G62" s="6">
         <f>_xlfn.XLOOKUP(A62,'[1]PFV Proyecto Puro'!D$3:D$78,'[1]PFV Proyecto Puro'!CE$3:CE$78,"---",0,1)</f>
         <v>20.753233477563935</v>
       </c>
-      <c r="G62">
+      <c r="H62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!H$28:H$760,"---",0,1)</f>
         <v>1</v>
       </c>
-      <c r="H62">
+      <c r="I62">
         <f>_xlfn.XLOOKUP(A62,'[1]SCORE comercial'!A$28:A$760,'[1]SCORE comercial'!K$28:K$760,"---",0,1)</f>
         <v>1</v>
       </c>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://wopi.dropbox.com/wopi/files/oid_11358078367124219904/WOPIServiceId_TP_DROPBOX_PLUS/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="20" documentId="13_ncr:1_{56F275FB-DE7A-43AA-BAAA-674B50A9D6B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A35A96BD-E9C8-4CA5-868B-A2182E30CE54}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F755FE5-B1C9-4684-A8FA-56C24E3F5E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Ranking PFV" sheetId="5" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -254,14 +254,20 @@
   <si>
     <t>¿Tiene BESS?</t>
   </si>
+  <si>
+    <t>Construcción</t>
+  </si>
+  <si>
+    <t>Autorizado Const.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="42" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="164" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
+    <numFmt numFmtId="164" formatCode="_ &quot;$&quot;* #,##0_ ;_ &quot;$&quot;* \-#,##0_ ;_ &quot;$&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="#,##0.00_ ;\-#,##0.00\ "/>
   </numFmts>
   <fonts count="5" x14ac:knownFonts="1">
     <font>
@@ -380,7 +386,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -394,13 +400,13 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="5" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -16461,19 +16467,19 @@
     <tabColor rgb="FF7030A0"/>
   </sheetPr>
   <dimension ref="A1:I62"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="47.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="47.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="7" width="16.28515625" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" customWidth="1"/>
+    <col min="5" max="5" width="14.5546875" customWidth="1"/>
+    <col min="6" max="7" width="16.33203125" customWidth="1"/>
     <col min="8" max="8" width="13" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
@@ -16502,7 +16508,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>60</v>
       </c>
@@ -16539,7 +16545,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>58</v>
       </c>
@@ -16576,7 +16582,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>53</v>
       </c>
@@ -16613,7 +16619,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
@@ -16650,7 +16656,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -16687,7 +16693,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>52</v>
       </c>
@@ -16724,7 +16730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>2</v>
       </c>
@@ -16761,7 +16767,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -16798,7 +16804,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -16806,9 +16812,8 @@
         <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENLIGHT INVESTMENTS SPA</v>
       </c>
-      <c r="C10" t="str">
-        <f>_xlfn.XLOOKUP(A10,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C10" t="s">
+        <v>71</v>
       </c>
       <c r="D10">
         <f>_xlfn.XLOOKUP(A10,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -16835,7 +16840,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>4</v>
       </c>
@@ -16872,7 +16877,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -16909,7 +16914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -16946,7 +16951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>9</v>
       </c>
@@ -16983,7 +16988,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>6</v>
       </c>
@@ -17020,7 +17025,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -17028,9 +17033,8 @@
         <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C16" t="str">
-        <f>_xlfn.XLOOKUP(A16,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C16" t="s">
+        <v>70</v>
       </c>
       <c r="D16">
         <f>_xlfn.XLOOKUP(A16,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -17057,7 +17061,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -17094,7 +17098,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>3</v>
       </c>
@@ -17131,7 +17135,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -17168,7 +17172,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -17205,7 +17209,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>57</v>
       </c>
@@ -17242,7 +17246,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>8</v>
       </c>
@@ -17279,7 +17283,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>36</v>
       </c>
@@ -17316,7 +17320,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>14</v>
       </c>
@@ -17353,7 +17357,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -17390,7 +17394,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>47</v>
       </c>
@@ -17427,7 +17431,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>13</v>
       </c>
@@ -17464,7 +17468,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -17501,7 +17505,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -17538,7 +17542,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>39</v>
       </c>
@@ -17575,7 +17579,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>22</v>
       </c>
@@ -17612,7 +17616,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>5</v>
       </c>
@@ -17649,7 +17653,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -17686,7 +17690,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>38</v>
       </c>
@@ -17723,7 +17727,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>35</v>
       </c>
@@ -17760,7 +17764,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>20</v>
       </c>
@@ -17797,7 +17801,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>23</v>
       </c>
@@ -17834,7 +17838,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>21</v>
       </c>
@@ -17871,7 +17875,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1</v>
       </c>
@@ -17908,7 +17912,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>30</v>
       </c>
@@ -17945,7 +17949,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>25</v>
       </c>
@@ -17982,7 +17986,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>59</v>
       </c>
@@ -18019,7 +18023,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>34</v>
       </c>
@@ -18056,7 +18060,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>55</v>
       </c>
@@ -18093,7 +18097,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>31</v>
       </c>
@@ -18130,7 +18134,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -18167,7 +18171,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>11</v>
       </c>
@@ -18204,7 +18208,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>32</v>
       </c>
@@ -18241,7 +18245,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>33</v>
       </c>
@@ -18278,7 +18282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>40</v>
       </c>
@@ -18315,7 +18319,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -18352,7 +18356,7 @@
         <v>-</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -18389,7 +18393,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>37</v>
       </c>
@@ -18426,7 +18430,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>48</v>
       </c>
@@ -18463,7 +18467,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>43</v>
       </c>
@@ -18500,7 +18504,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>41</v>
       </c>
@@ -18537,7 +18541,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>45</v>
       </c>
@@ -18574,7 +18578,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>49</v>
       </c>
@@ -18611,7 +18615,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>46</v>
       </c>
@@ -18648,7 +18652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -18685,7 +18689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>51</v>
       </c>
@@ -18722,7 +18726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>56</v>
       </c>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F755FE5-B1C9-4684-A8FA-56C24E3F5E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE52A8-1216-48DD-A47B-2ACCB81B7B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -258,7 +258,7 @@
     <t>Construcción</t>
   </si>
   <si>
-    <t>Autorizado Const.</t>
+    <t>Autorizado Construcción</t>
   </si>
 </sst>
 </file>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1CE52A8-1216-48DD-A47B-2ACCB81B7B3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DFD6F5-1B2A-4EC1-AE94-7ABA1E6CF9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -16996,9 +16996,8 @@
         <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>JAVIERA SPA</v>
       </c>
-      <c r="C15" t="str">
-        <f>_xlfn.XLOOKUP(A15,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C15" t="s">
+        <v>71</v>
       </c>
       <c r="D15">
         <f>_xlfn.XLOOKUP(A15,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46DFD6F5-1B2A-4EC1-AE94-7ABA1E6CF9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2693B93B-EB29-4719-B2B0-1A465D741679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -16922,9 +16922,8 @@
         <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CHUNGUNGO S.A.</v>
       </c>
-      <c r="C13" t="str">
-        <f>_xlfn.XLOOKUP(A13,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C13" t="s">
+        <v>71</v>
       </c>
       <c r="D13">
         <f>_xlfn.XLOOKUP(A13,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2693B93B-EB29-4719-B2B0-1A465D741679}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122B9B79-AEF1-42EE-8A35-B80B40B6FAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -17474,9 +17474,8 @@
         <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C28" t="str">
-        <f>_xlfn.XLOOKUP(A28,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C28" t="s">
+        <v>71</v>
       </c>
       <c r="D28">
         <f>_xlfn.XLOOKUP(A28,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>

--- a/BD Centrales - Extra.xlsx
+++ b/BD Centrales - Extra.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bryan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{122B9B79-AEF1-42EE-8A35-B80B40B6FAF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49C1BD0F-51BE-4F6D-8181-739EF519ED23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="73">
   <si>
     <t>PFV LLANO DE LLAMPOS</t>
   </si>
@@ -259,6 +259,9 @@
   </si>
   <si>
     <t>Autorizado Construcción</t>
+  </si>
+  <si>
+    <t>Proceso SAC</t>
   </si>
 </sst>
 </file>
@@ -17510,9 +17513,8 @@
         <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CONEJO SOLAR SPA</v>
       </c>
-      <c r="C29" t="str">
-        <f>_xlfn.XLOOKUP(A29,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C29" t="s">
+        <v>71</v>
       </c>
       <c r="D29">
         <f>_xlfn.XLOOKUP(A29,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -17695,9 +17697,8 @@
         <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C34" t="str">
-        <f>_xlfn.XLOOKUP(A34,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C34" t="s">
+        <v>71</v>
       </c>
       <c r="D34">
         <f>_xlfn.XLOOKUP(A34,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -17954,9 +17955,8 @@
         <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ACCIONA ENERGÍA CHILE HOLDINGS S.A.</v>
       </c>
-      <c r="C41" t="str">
-        <f>_xlfn.XLOOKUP(A41,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C41" t="s">
+        <v>71</v>
       </c>
       <c r="D41">
         <f>_xlfn.XLOOKUP(A41,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18028,9 +18028,8 @@
         <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>CÓNDOR ENERGÍA SPA</v>
       </c>
-      <c r="C43" t="str">
-        <f>_xlfn.XLOOKUP(A43,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C43" t="s">
+        <v>71</v>
       </c>
       <c r="D43">
         <f>_xlfn.XLOOKUP(A43,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18065,9 +18064,8 @@
         <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>PARQUE SOLAR LEYDA SPA</v>
       </c>
-      <c r="C44" t="str">
-        <f>_xlfn.XLOOKUP(A44,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C44" t="s">
+        <v>72</v>
       </c>
       <c r="D44">
         <f>_xlfn.XLOOKUP(A44,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18287,9 +18285,8 @@
         <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>HUEMUL ENERGÍA SPA</v>
       </c>
-      <c r="C50" t="str">
-        <f>_xlfn.XLOOKUP(A50,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C50" t="s">
+        <v>71</v>
       </c>
       <c r="D50">
         <f>_xlfn.XLOOKUP(A50,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18398,9 +18395,8 @@
         <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>FOTOVOLTAICA NORTE GRANDE 5 SPA</v>
       </c>
-      <c r="C53" t="str">
-        <f>_xlfn.XLOOKUP(A53,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C53" t="s">
+        <v>71</v>
       </c>
       <c r="D53">
         <f>_xlfn.XLOOKUP(A53,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18435,9 +18431,8 @@
         <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>SONNEDIX COX ENERGY CHILE SPA</v>
       </c>
-      <c r="C54" t="str">
-        <f>_xlfn.XLOOKUP(A54,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C54" t="s">
+        <v>71</v>
       </c>
       <c r="D54">
         <f>_xlfn.XLOOKUP(A54,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18472,9 +18467,8 @@
         <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>ENEL GREEN POWER CHILE S.A.</v>
       </c>
-      <c r="C55" t="str">
-        <f>_xlfn.XLOOKUP(A55,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C55" t="s">
+        <v>70</v>
       </c>
       <c r="D55">
         <f>_xlfn.XLOOKUP(A55,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
@@ -18509,9 +18503,8 @@
         <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$C$3:$C$78,"---",0,1)</f>
         <v>HUEMUL ENERGÍA SPA</v>
       </c>
-      <c r="C56" t="str">
-        <f>_xlfn.XLOOKUP(A56,'[1]PFV Proyecto Puro'!$D$3:$D$78,'[1]PFV Proyecto Puro'!$M$3:$M$78,"---",0,1)</f>
-        <v>-</v>
+      <c r="C56" t="s">
+        <v>72</v>
       </c>
       <c r="D56">
         <f>_xlfn.XLOOKUP(A56,'[1]SCORE Técnico 2025'!A$28:A$88,'[1]SCORE Técnico 2025'!M$28:M$88,"---",0,1)</f>
